--- a/docs/gantt-charts/IT Capstone Project - Quarter 3.xlsx
+++ b/docs/gantt-charts/IT Capstone Project - Quarter 3.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30619"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8F2E6B0-D5AA-44DC-A6D9-B14F2C768EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA55F5EC-9FCB-4D35-822D-D6DE7353E516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
   <si>
     <t>Project Start Date:</t>
   </si>
@@ -123,27 +123,30 @@
     <t>Sept-22-2026</t>
   </si>
   <si>
+    <t>Oct-13-2026</t>
+  </si>
+  <si>
+    <t>AI - Connect to Gemini API</t>
+  </si>
+  <si>
+    <t>Sept-18-2026</t>
+  </si>
+  <si>
+    <t>Oct-8-2026</t>
+  </si>
+  <si>
+    <t>AI - User confirmation screen</t>
+  </si>
+  <si>
+    <t>Oct-6-2026</t>
+  </si>
+  <si>
     <t>TBD</t>
   </si>
   <si>
     <t>In Progress</t>
   </si>
   <si>
-    <t>AI - Connect to Gemini API</t>
-  </si>
-  <si>
-    <t>Sept-18-2026</t>
-  </si>
-  <si>
-    <t>Oct-8-2026</t>
-  </si>
-  <si>
-    <t>AI - User confirmation screen</t>
-  </si>
-  <si>
-    <t>Oct-6-2026</t>
-  </si>
-  <si>
     <t>AI - Validate structured output</t>
   </si>
   <si>
@@ -177,9 +180,15 @@
     <t>Sept-15-2026</t>
   </si>
   <si>
+    <t>Oct-16-2026</t>
+  </si>
+  <si>
     <t>Transaction entry &amp; forms</t>
   </si>
   <si>
+    <t>Oct-5-2026</t>
+  </si>
+  <si>
     <t>Project Foundation - Repo &amp; branch structure</t>
   </si>
   <si>
@@ -219,13 +228,13 @@
     <t>Environment config &amp; setup</t>
   </si>
   <si>
+    <t>Web Deployment</t>
+  </si>
+  <si>
+    <t>Jensen/Steeve</t>
+  </si>
+  <si>
     <t>Not Started</t>
-  </si>
-  <si>
-    <t>Web Deployment</t>
-  </si>
-  <si>
-    <t>Jensen/Steeve</t>
   </si>
   <si>
     <t>Web Design</t>
@@ -274,7 +283,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,6 +348,12 @@
     <font>
       <sz val="20"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
       <name val="Aptos Display"/>
       <charset val="1"/>
     </font>
@@ -606,7 +621,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -846,12 +861,12 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -859,6 +874,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1216,38 +1237,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="8.25" customHeight="1">
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
     </row>
     <row r="2" spans="1:24" ht="18.75" customHeight="1">
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
       <c r="K2" s="84">
         <v>2026</v>
       </c>
@@ -1278,7 +1299,7 @@
       <c r="G3" s="25"/>
       <c r="H3" s="25"/>
       <c r="I3" s="28"/>
-      <c r="J3" s="81"/>
+      <c r="J3" s="82"/>
       <c r="K3" s="85" t="s">
         <v>1</v>
       </c>
@@ -1319,7 +1340,7 @@
       <c r="I4" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="81"/>
+      <c r="J4" s="82"/>
       <c r="K4" s="1">
         <f>D3</f>
         <v>46269</v>
@@ -1566,13 +1587,13 @@
         <v>29</v>
       </c>
       <c r="G9" s="38">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I9" s="77">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J9" s="18"/>
       <c r="K9" s="9"/>
@@ -1580,9 +1601,11 @@
       <c r="M9" s="66"/>
       <c r="N9" s="66"/>
       <c r="O9" s="66"/>
-      <c r="P9" s="66"/>
-      <c r="Q9" s="66"/>
-      <c r="R9" s="66"/>
+      <c r="P9" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="86"/>
+      <c r="R9" s="86"/>
       <c r="S9" s="9"/>
       <c r="T9" s="9"/>
       <c r="U9" s="8"/>
@@ -1596,16 +1619,16 @@
         <v>5</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="34" t="s">
         <v>32</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>33</v>
       </c>
       <c r="G10" s="38">
         <v>18</v>
@@ -1614,7 +1637,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="69">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J10" s="18"/>
       <c r="K10" s="9"/>
@@ -1640,31 +1663,33 @@
         <v>6</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="38"/>
+      <c r="G11" s="38">
+        <v>23</v>
+      </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I11" s="77">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J11" s="18"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
+      <c r="O11" s="66"/>
+      <c r="P11" s="66"/>
       <c r="Q11" s="66"/>
       <c r="R11" s="66"/>
       <c r="S11" s="9"/>
@@ -1680,7 +1705,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>27</v>
@@ -1689,7 +1714,7 @@
         <v>28</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="38">
         <v>14</v>
@@ -1698,7 +1723,7 @@
         <v>20</v>
       </c>
       <c r="I12" s="69">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="9"/>
@@ -1724,22 +1749,22 @@
         <v>8</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G13" s="38">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I13" s="77">
         <v>0.8</v>
@@ -1766,16 +1791,16 @@
         <v>9</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G14" s="38">
         <v>1</v>
@@ -1810,25 +1835,25 @@
         <v>10</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="38">
         <v>43</v>
       </c>
-      <c r="F15" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="38">
-        <v>42</v>
-      </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I15" s="77">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="J15" s="18"/>
       <c r="K15" s="9"/>
@@ -1852,25 +1877,25 @@
         <v>11</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
       <c r="E16" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="38">
         <v>43</v>
       </c>
-      <c r="F16" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="38">
-        <v>42</v>
-      </c>
       <c r="H16" s="12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I16" s="69">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J16" s="18"/>
       <c r="K16" s="9"/>
@@ -1894,25 +1919,25 @@
         <v>12</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G17" s="38">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I17" s="77">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J17" s="18"/>
       <c r="K17" s="9"/>
@@ -1921,94 +1946,96 @@
       <c r="N17" s="66"/>
       <c r="O17" s="66"/>
       <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
+      <c r="Q17" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" s="86"/>
       <c r="S17" s="9"/>
       <c r="T17" s="9"/>
       <c r="U17" s="8"/>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AA17" s="81"/>
-      <c r="AB17" s="81"/>
-      <c r="AC17" s="81"/>
-      <c r="AD17" s="81"/>
-      <c r="AE17" s="81"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="81"/>
-      <c r="AI17" s="81"/>
-      <c r="AJ17" s="81"/>
-      <c r="AK17" s="81"/>
-      <c r="AL17" s="81"/>
-      <c r="AM17" s="81"/>
-      <c r="AN17" s="81"/>
-      <c r="AO17" s="81"/>
-      <c r="AP17" s="81"/>
-      <c r="AQ17" s="81"/>
-      <c r="AR17" s="81"/>
-      <c r="AS17" s="81"/>
-      <c r="AT17" s="81"/>
-      <c r="AU17" s="81"/>
-      <c r="AV17" s="81"/>
-      <c r="AW17" s="81"/>
-      <c r="AX17" s="81"/>
-      <c r="AY17" s="81"/>
-      <c r="AZ17" s="81"/>
-      <c r="BA17" s="81"/>
-      <c r="BB17" s="81"/>
-      <c r="BC17" s="81"/>
-      <c r="BD17" s="81"/>
-      <c r="BE17" s="81"/>
-      <c r="BF17" s="81"/>
-      <c r="BG17" s="81"/>
-      <c r="BH17" s="81"/>
-      <c r="BI17" s="81"/>
-      <c r="BJ17" s="81"/>
-      <c r="BK17" s="81"/>
-      <c r="BL17" s="81"/>
-      <c r="BM17" s="81"/>
-      <c r="BN17" s="81"/>
-      <c r="BO17" s="81"/>
-      <c r="BP17" s="81"/>
-      <c r="BQ17" s="81"/>
-      <c r="BR17" s="81"/>
-      <c r="BS17" s="81"/>
-      <c r="BT17" s="81"/>
-      <c r="BU17" s="81"/>
-      <c r="BV17" s="81"/>
-      <c r="BW17" s="81"/>
-      <c r="BX17" s="81"/>
-      <c r="BY17" s="81"/>
-      <c r="BZ17" s="81"/>
-      <c r="CA17" s="81"/>
-      <c r="CB17" s="81"/>
-      <c r="CC17" s="81"/>
-      <c r="CD17" s="81"/>
-      <c r="CE17" s="81"/>
-      <c r="CF17" s="81"/>
-      <c r="CG17" s="81"/>
-      <c r="CH17" s="81"/>
-      <c r="CI17" s="81"/>
-      <c r="CJ17" s="81"/>
-      <c r="CK17" s="81"/>
-      <c r="CL17" s="81"/>
-      <c r="CM17" s="81"/>
-      <c r="CN17" s="81"/>
-      <c r="CO17" s="81"/>
-      <c r="CP17" s="81"/>
-      <c r="CQ17" s="81"/>
-      <c r="CR17" s="81"/>
-      <c r="CS17" s="81"/>
-      <c r="CT17" s="81"/>
-      <c r="CU17" s="81"/>
-      <c r="CV17" s="81"/>
-      <c r="CW17" s="81"/>
-      <c r="CX17" s="81"/>
-      <c r="CY17" s="81"/>
-      <c r="CZ17" s="81"/>
+      <c r="Y17" s="82"/>
+      <c r="Z17" s="82"/>
+      <c r="AA17" s="82"/>
+      <c r="AB17" s="82"/>
+      <c r="AC17" s="82"/>
+      <c r="AD17" s="82"/>
+      <c r="AE17" s="82"/>
+      <c r="AF17" s="82"/>
+      <c r="AG17" s="82"/>
+      <c r="AH17" s="82"/>
+      <c r="AI17" s="82"/>
+      <c r="AJ17" s="82"/>
+      <c r="AK17" s="82"/>
+      <c r="AL17" s="82"/>
+      <c r="AM17" s="82"/>
+      <c r="AN17" s="82"/>
+      <c r="AO17" s="82"/>
+      <c r="AP17" s="82"/>
+      <c r="AQ17" s="82"/>
+      <c r="AR17" s="82"/>
+      <c r="AS17" s="82"/>
+      <c r="AT17" s="82"/>
+      <c r="AU17" s="82"/>
+      <c r="AV17" s="82"/>
+      <c r="AW17" s="82"/>
+      <c r="AX17" s="82"/>
+      <c r="AY17" s="82"/>
+      <c r="AZ17" s="82"/>
+      <c r="BA17" s="82"/>
+      <c r="BB17" s="82"/>
+      <c r="BC17" s="82"/>
+      <c r="BD17" s="82"/>
+      <c r="BE17" s="82"/>
+      <c r="BF17" s="82"/>
+      <c r="BG17" s="82"/>
+      <c r="BH17" s="82"/>
+      <c r="BI17" s="82"/>
+      <c r="BJ17" s="82"/>
+      <c r="BK17" s="82"/>
+      <c r="BL17" s="82"/>
+      <c r="BM17" s="82"/>
+      <c r="BN17" s="82"/>
+      <c r="BO17" s="82"/>
+      <c r="BP17" s="82"/>
+      <c r="BQ17" s="82"/>
+      <c r="BR17" s="82"/>
+      <c r="BS17" s="82"/>
+      <c r="BT17" s="82"/>
+      <c r="BU17" s="82"/>
+      <c r="BV17" s="82"/>
+      <c r="BW17" s="82"/>
+      <c r="BX17" s="82"/>
+      <c r="BY17" s="82"/>
+      <c r="BZ17" s="82"/>
+      <c r="CA17" s="82"/>
+      <c r="CB17" s="82"/>
+      <c r="CC17" s="82"/>
+      <c r="CD17" s="82"/>
+      <c r="CE17" s="82"/>
+      <c r="CF17" s="82"/>
+      <c r="CG17" s="82"/>
+      <c r="CH17" s="82"/>
+      <c r="CI17" s="82"/>
+      <c r="CJ17" s="82"/>
+      <c r="CK17" s="82"/>
+      <c r="CL17" s="82"/>
+      <c r="CM17" s="82"/>
+      <c r="CN17" s="82"/>
+      <c r="CO17" s="82"/>
+      <c r="CP17" s="82"/>
+      <c r="CQ17" s="82"/>
+      <c r="CR17" s="82"/>
+      <c r="CS17" s="82"/>
+      <c r="CT17" s="82"/>
+      <c r="CU17" s="82"/>
+      <c r="CV17" s="82"/>
+      <c r="CW17" s="82"/>
+      <c r="CX17" s="82"/>
+      <c r="CY17" s="82"/>
+      <c r="CZ17" s="82"/>
     </row>
     <row r="18" spans="1:104" ht="35.25" customHeight="1">
       <c r="A18"/>
@@ -2016,7 +2043,7 @@
         <v>13</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>27</v>
@@ -2025,13 +2052,13 @@
         <v>28</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="G18" s="38">
+        <v>37</v>
+      </c>
+      <c r="H18" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>30</v>
       </c>
       <c r="I18" s="78">
         <v>0.5</v>
@@ -2042,95 +2069,97 @@
       <c r="M18" s="66"/>
       <c r="N18" s="66"/>
       <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
+      <c r="P18" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q18" s="86"/>
+      <c r="R18" s="86"/>
       <c r="S18" s="9"/>
       <c r="T18" s="9"/>
       <c r="U18" s="8"/>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
-      <c r="Y18" s="81"/>
-      <c r="Z18" s="81"/>
-      <c r="AA18" s="81"/>
-      <c r="AB18" s="81"/>
-      <c r="AC18" s="81"/>
-      <c r="AD18" s="81"/>
-      <c r="AE18" s="81"/>
-      <c r="AF18" s="81"/>
-      <c r="AG18" s="81"/>
-      <c r="AH18" s="81"/>
-      <c r="AI18" s="81"/>
-      <c r="AJ18" s="81"/>
-      <c r="AK18" s="81"/>
-      <c r="AL18" s="81"/>
-      <c r="AM18" s="81"/>
-      <c r="AN18" s="81"/>
-      <c r="AO18" s="81"/>
-      <c r="AP18" s="81"/>
-      <c r="AQ18" s="81"/>
-      <c r="AR18" s="81"/>
-      <c r="AS18" s="81"/>
-      <c r="AT18" s="81"/>
-      <c r="AU18" s="81"/>
-      <c r="AV18" s="81"/>
-      <c r="AW18" s="81"/>
-      <c r="AX18" s="81"/>
-      <c r="AY18" s="81"/>
-      <c r="AZ18" s="81"/>
-      <c r="BA18" s="81"/>
-      <c r="BB18" s="81"/>
-      <c r="BC18" s="81"/>
-      <c r="BD18" s="81"/>
-      <c r="BE18" s="81"/>
-      <c r="BF18" s="81"/>
-      <c r="BG18" s="81"/>
-      <c r="BH18" s="81"/>
-      <c r="BI18" s="81"/>
-      <c r="BJ18" s="81"/>
-      <c r="BK18" s="81"/>
-      <c r="BL18" s="81"/>
-      <c r="BM18" s="81"/>
-      <c r="BN18" s="81"/>
-      <c r="BO18" s="81"/>
-      <c r="BP18" s="81"/>
-      <c r="BQ18" s="81"/>
-      <c r="BR18" s="81"/>
-      <c r="BS18" s="81"/>
-      <c r="BT18" s="81"/>
-      <c r="BU18" s="81"/>
-      <c r="BV18" s="81"/>
-      <c r="BW18" s="81"/>
-      <c r="BX18" s="81"/>
-      <c r="BY18" s="81"/>
-      <c r="BZ18" s="81"/>
-      <c r="CA18" s="81"/>
-      <c r="CB18" s="81"/>
-      <c r="CC18" s="81"/>
-      <c r="CD18" s="81"/>
-      <c r="CE18" s="81"/>
-      <c r="CF18" s="81"/>
-      <c r="CG18" s="81"/>
-      <c r="CH18" s="81"/>
-      <c r="CI18" s="81"/>
-      <c r="CJ18" s="81"/>
-      <c r="CK18" s="81"/>
-      <c r="CL18" s="81"/>
-      <c r="CM18" s="81"/>
-      <c r="CN18" s="81"/>
-      <c r="CO18" s="81"/>
-      <c r="CP18" s="81"/>
-      <c r="CQ18" s="81"/>
-      <c r="CR18" s="81"/>
-      <c r="CS18" s="81"/>
-      <c r="CT18" s="81"/>
-      <c r="CU18" s="81"/>
-      <c r="CV18" s="81"/>
-      <c r="CW18" s="81"/>
-      <c r="CX18" s="81"/>
-      <c r="CY18" s="81"/>
-      <c r="CZ18" s="81"/>
+      <c r="Y18" s="82"/>
+      <c r="Z18" s="82"/>
+      <c r="AA18" s="82"/>
+      <c r="AB18" s="82"/>
+      <c r="AC18" s="82"/>
+      <c r="AD18" s="82"/>
+      <c r="AE18" s="82"/>
+      <c r="AF18" s="82"/>
+      <c r="AG18" s="82"/>
+      <c r="AH18" s="82"/>
+      <c r="AI18" s="82"/>
+      <c r="AJ18" s="82"/>
+      <c r="AK18" s="82"/>
+      <c r="AL18" s="82"/>
+      <c r="AM18" s="82"/>
+      <c r="AN18" s="82"/>
+      <c r="AO18" s="82"/>
+      <c r="AP18" s="82"/>
+      <c r="AQ18" s="82"/>
+      <c r="AR18" s="82"/>
+      <c r="AS18" s="82"/>
+      <c r="AT18" s="82"/>
+      <c r="AU18" s="82"/>
+      <c r="AV18" s="82"/>
+      <c r="AW18" s="82"/>
+      <c r="AX18" s="82"/>
+      <c r="AY18" s="82"/>
+      <c r="AZ18" s="82"/>
+      <c r="BA18" s="82"/>
+      <c r="BB18" s="82"/>
+      <c r="BC18" s="82"/>
+      <c r="BD18" s="82"/>
+      <c r="BE18" s="82"/>
+      <c r="BF18" s="82"/>
+      <c r="BG18" s="82"/>
+      <c r="BH18" s="82"/>
+      <c r="BI18" s="82"/>
+      <c r="BJ18" s="82"/>
+      <c r="BK18" s="82"/>
+      <c r="BL18" s="82"/>
+      <c r="BM18" s="82"/>
+      <c r="BN18" s="82"/>
+      <c r="BO18" s="82"/>
+      <c r="BP18" s="82"/>
+      <c r="BQ18" s="82"/>
+      <c r="BR18" s="82"/>
+      <c r="BS18" s="82"/>
+      <c r="BT18" s="82"/>
+      <c r="BU18" s="82"/>
+      <c r="BV18" s="82"/>
+      <c r="BW18" s="82"/>
+      <c r="BX18" s="82"/>
+      <c r="BY18" s="82"/>
+      <c r="BZ18" s="82"/>
+      <c r="CA18" s="82"/>
+      <c r="CB18" s="82"/>
+      <c r="CC18" s="82"/>
+      <c r="CD18" s="82"/>
+      <c r="CE18" s="82"/>
+      <c r="CF18" s="82"/>
+      <c r="CG18" s="82"/>
+      <c r="CH18" s="82"/>
+      <c r="CI18" s="82"/>
+      <c r="CJ18" s="82"/>
+      <c r="CK18" s="82"/>
+      <c r="CL18" s="82"/>
+      <c r="CM18" s="82"/>
+      <c r="CN18" s="82"/>
+      <c r="CO18" s="82"/>
+      <c r="CP18" s="82"/>
+      <c r="CQ18" s="82"/>
+      <c r="CR18" s="82"/>
+      <c r="CS18" s="82"/>
+      <c r="CT18" s="82"/>
+      <c r="CU18" s="82"/>
+      <c r="CV18" s="82"/>
+      <c r="CW18" s="82"/>
+      <c r="CX18" s="82"/>
+      <c r="CY18" s="82"/>
+      <c r="CZ18" s="82"/>
     </row>
     <row r="19" spans="1:104" ht="35.25" customHeight="1">
       <c r="A19"/>
@@ -2138,16 +2167,16 @@
         <v>14</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E19" s="65" t="s">
         <v>19</v>
       </c>
       <c r="F19" s="45" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G19" s="38">
         <v>20</v>
@@ -2175,86 +2204,86 @@
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="81"/>
-      <c r="AA19" s="81"/>
-      <c r="AB19" s="81"/>
-      <c r="AC19" s="81"/>
-      <c r="AD19" s="81"/>
-      <c r="AE19" s="81"/>
-      <c r="AF19" s="81"/>
-      <c r="AG19" s="81"/>
-      <c r="AH19" s="81"/>
-      <c r="AI19" s="81"/>
-      <c r="AJ19" s="81"/>
-      <c r="AK19" s="81"/>
-      <c r="AL19" s="81"/>
-      <c r="AM19" s="81"/>
-      <c r="AN19" s="81"/>
-      <c r="AO19" s="81"/>
-      <c r="AP19" s="81"/>
-      <c r="AQ19" s="81"/>
-      <c r="AR19" s="81"/>
-      <c r="AS19" s="81"/>
-      <c r="AT19" s="81"/>
-      <c r="AU19" s="81"/>
-      <c r="AV19" s="81"/>
-      <c r="AW19" s="81"/>
-      <c r="AX19" s="81"/>
-      <c r="AY19" s="81"/>
-      <c r="AZ19" s="81"/>
-      <c r="BA19" s="81"/>
-      <c r="BB19" s="81"/>
-      <c r="BC19" s="81"/>
-      <c r="BD19" s="81"/>
-      <c r="BE19" s="81"/>
-      <c r="BF19" s="81"/>
-      <c r="BG19" s="81"/>
-      <c r="BH19" s="81"/>
-      <c r="BI19" s="81"/>
-      <c r="BJ19" s="81"/>
-      <c r="BK19" s="81"/>
-      <c r="BL19" s="81"/>
-      <c r="BM19" s="81"/>
-      <c r="BN19" s="81"/>
-      <c r="BO19" s="81"/>
-      <c r="BP19" s="81"/>
-      <c r="BQ19" s="81"/>
-      <c r="BR19" s="81"/>
-      <c r="BS19" s="81"/>
-      <c r="BT19" s="81"/>
-      <c r="BU19" s="81"/>
-      <c r="BV19" s="81"/>
-      <c r="BW19" s="81"/>
-      <c r="BX19" s="81"/>
-      <c r="BY19" s="81"/>
-      <c r="BZ19" s="81"/>
-      <c r="CA19" s="81"/>
-      <c r="CB19" s="81"/>
-      <c r="CC19" s="81"/>
-      <c r="CD19" s="81"/>
-      <c r="CE19" s="81"/>
-      <c r="CF19" s="81"/>
-      <c r="CG19" s="81"/>
-      <c r="CH19" s="81"/>
-      <c r="CI19" s="81"/>
-      <c r="CJ19" s="81"/>
-      <c r="CK19" s="81"/>
-      <c r="CL19" s="81"/>
-      <c r="CM19" s="81"/>
-      <c r="CN19" s="81"/>
-      <c r="CO19" s="81"/>
-      <c r="CP19" s="81"/>
-      <c r="CQ19" s="81"/>
-      <c r="CR19" s="81"/>
-      <c r="CS19" s="81"/>
-      <c r="CT19" s="81"/>
-      <c r="CU19" s="81"/>
-      <c r="CV19" s="81"/>
-      <c r="CW19" s="81"/>
-      <c r="CX19" s="81"/>
-      <c r="CY19" s="81"/>
-      <c r="CZ19" s="81"/>
+      <c r="Y19" s="82"/>
+      <c r="Z19" s="82"/>
+      <c r="AA19" s="82"/>
+      <c r="AB19" s="82"/>
+      <c r="AC19" s="82"/>
+      <c r="AD19" s="82"/>
+      <c r="AE19" s="82"/>
+      <c r="AF19" s="82"/>
+      <c r="AG19" s="82"/>
+      <c r="AH19" s="82"/>
+      <c r="AI19" s="82"/>
+      <c r="AJ19" s="82"/>
+      <c r="AK19" s="82"/>
+      <c r="AL19" s="82"/>
+      <c r="AM19" s="82"/>
+      <c r="AN19" s="82"/>
+      <c r="AO19" s="82"/>
+      <c r="AP19" s="82"/>
+      <c r="AQ19" s="82"/>
+      <c r="AR19" s="82"/>
+      <c r="AS19" s="82"/>
+      <c r="AT19" s="82"/>
+      <c r="AU19" s="82"/>
+      <c r="AV19" s="82"/>
+      <c r="AW19" s="82"/>
+      <c r="AX19" s="82"/>
+      <c r="AY19" s="82"/>
+      <c r="AZ19" s="82"/>
+      <c r="BA19" s="82"/>
+      <c r="BB19" s="82"/>
+      <c r="BC19" s="82"/>
+      <c r="BD19" s="82"/>
+      <c r="BE19" s="82"/>
+      <c r="BF19" s="82"/>
+      <c r="BG19" s="82"/>
+      <c r="BH19" s="82"/>
+      <c r="BI19" s="82"/>
+      <c r="BJ19" s="82"/>
+      <c r="BK19" s="82"/>
+      <c r="BL19" s="82"/>
+      <c r="BM19" s="82"/>
+      <c r="BN19" s="82"/>
+      <c r="BO19" s="82"/>
+      <c r="BP19" s="82"/>
+      <c r="BQ19" s="82"/>
+      <c r="BR19" s="82"/>
+      <c r="BS19" s="82"/>
+      <c r="BT19" s="82"/>
+      <c r="BU19" s="82"/>
+      <c r="BV19" s="82"/>
+      <c r="BW19" s="82"/>
+      <c r="BX19" s="82"/>
+      <c r="BY19" s="82"/>
+      <c r="BZ19" s="82"/>
+      <c r="CA19" s="82"/>
+      <c r="CB19" s="82"/>
+      <c r="CC19" s="82"/>
+      <c r="CD19" s="82"/>
+      <c r="CE19" s="82"/>
+      <c r="CF19" s="82"/>
+      <c r="CG19" s="82"/>
+      <c r="CH19" s="82"/>
+      <c r="CI19" s="82"/>
+      <c r="CJ19" s="82"/>
+      <c r="CK19" s="82"/>
+      <c r="CL19" s="82"/>
+      <c r="CM19" s="82"/>
+      <c r="CN19" s="82"/>
+      <c r="CO19" s="82"/>
+      <c r="CP19" s="82"/>
+      <c r="CQ19" s="82"/>
+      <c r="CR19" s="82"/>
+      <c r="CS19" s="82"/>
+      <c r="CT19" s="82"/>
+      <c r="CU19" s="82"/>
+      <c r="CV19" s="82"/>
+      <c r="CW19" s="82"/>
+      <c r="CX19" s="82"/>
+      <c r="CY19" s="82"/>
+      <c r="CZ19" s="82"/>
     </row>
     <row r="20" spans="1:104" ht="35.25" customHeight="1">
       <c r="A20"/>
@@ -2262,16 +2291,16 @@
         <v>15</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="48" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G20" s="38">
         <v>5</v>
@@ -2299,86 +2328,86 @@
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
       <c r="X20" s="9"/>
-      <c r="Y20" s="81"/>
-      <c r="Z20" s="81"/>
-      <c r="AA20" s="81"/>
-      <c r="AB20" s="81"/>
-      <c r="AC20" s="81"/>
-      <c r="AD20" s="81"/>
-      <c r="AE20" s="81"/>
-      <c r="AF20" s="81"/>
-      <c r="AG20" s="81"/>
-      <c r="AH20" s="81"/>
-      <c r="AI20" s="81"/>
-      <c r="AJ20" s="81"/>
-      <c r="AK20" s="81"/>
-      <c r="AL20" s="81"/>
-      <c r="AM20" s="81"/>
-      <c r="AN20" s="81"/>
-      <c r="AO20" s="81"/>
-      <c r="AP20" s="81"/>
-      <c r="AQ20" s="81"/>
-      <c r="AR20" s="81"/>
-      <c r="AS20" s="81"/>
-      <c r="AT20" s="81"/>
-      <c r="AU20" s="81"/>
-      <c r="AV20" s="81"/>
-      <c r="AW20" s="81"/>
-      <c r="AX20" s="81"/>
-      <c r="AY20" s="81"/>
-      <c r="AZ20" s="81"/>
-      <c r="BA20" s="81"/>
-      <c r="BB20" s="81"/>
-      <c r="BC20" s="81"/>
-      <c r="BD20" s="81"/>
-      <c r="BE20" s="81"/>
-      <c r="BF20" s="81"/>
-      <c r="BG20" s="81"/>
-      <c r="BH20" s="81"/>
-      <c r="BI20" s="81"/>
-      <c r="BJ20" s="81"/>
-      <c r="BK20" s="81"/>
-      <c r="BL20" s="81"/>
-      <c r="BM20" s="81"/>
-      <c r="BN20" s="81"/>
-      <c r="BO20" s="81"/>
-      <c r="BP20" s="81"/>
-      <c r="BQ20" s="81"/>
-      <c r="BR20" s="81"/>
-      <c r="BS20" s="81"/>
-      <c r="BT20" s="81"/>
-      <c r="BU20" s="81"/>
-      <c r="BV20" s="81"/>
-      <c r="BW20" s="81"/>
-      <c r="BX20" s="81"/>
-      <c r="BY20" s="81"/>
-      <c r="BZ20" s="81"/>
-      <c r="CA20" s="81"/>
-      <c r="CB20" s="81"/>
-      <c r="CC20" s="81"/>
-      <c r="CD20" s="81"/>
-      <c r="CE20" s="81"/>
-      <c r="CF20" s="81"/>
-      <c r="CG20" s="81"/>
-      <c r="CH20" s="81"/>
-      <c r="CI20" s="81"/>
-      <c r="CJ20" s="81"/>
-      <c r="CK20" s="81"/>
-      <c r="CL20" s="81"/>
-      <c r="CM20" s="81"/>
-      <c r="CN20" s="81"/>
-      <c r="CO20" s="81"/>
-      <c r="CP20" s="81"/>
-      <c r="CQ20" s="81"/>
-      <c r="CR20" s="81"/>
-      <c r="CS20" s="81"/>
-      <c r="CT20" s="81"/>
-      <c r="CU20" s="81"/>
-      <c r="CV20" s="81"/>
-      <c r="CW20" s="81"/>
-      <c r="CX20" s="81"/>
-      <c r="CY20" s="81"/>
-      <c r="CZ20" s="81"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="82"/>
+      <c r="AA20" s="82"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
+      <c r="AE20" s="82"/>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="82"/>
+      <c r="AN20" s="82"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="82"/>
+      <c r="AQ20" s="82"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="82"/>
+      <c r="AT20" s="82"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="82"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="82"/>
+      <c r="AZ20" s="82"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="82"/>
+      <c r="BC20" s="82"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="82"/>
+      <c r="BF20" s="82"/>
+      <c r="BG20" s="82"/>
+      <c r="BH20" s="82"/>
+      <c r="BI20" s="82"/>
+      <c r="BJ20" s="82"/>
+      <c r="BK20" s="82"/>
+      <c r="BL20" s="82"/>
+      <c r="BM20" s="82"/>
+      <c r="BN20" s="82"/>
+      <c r="BO20" s="82"/>
+      <c r="BP20" s="82"/>
+      <c r="BQ20" s="82"/>
+      <c r="BR20" s="82"/>
+      <c r="BS20" s="82"/>
+      <c r="BT20" s="82"/>
+      <c r="BU20" s="82"/>
+      <c r="BV20" s="82"/>
+      <c r="BW20" s="82"/>
+      <c r="BX20" s="82"/>
+      <c r="BY20" s="82"/>
+      <c r="BZ20" s="82"/>
+      <c r="CA20" s="82"/>
+      <c r="CB20" s="82"/>
+      <c r="CC20" s="82"/>
+      <c r="CD20" s="82"/>
+      <c r="CE20" s="82"/>
+      <c r="CF20" s="82"/>
+      <c r="CG20" s="82"/>
+      <c r="CH20" s="82"/>
+      <c r="CI20" s="82"/>
+      <c r="CJ20" s="82"/>
+      <c r="CK20" s="82"/>
+      <c r="CL20" s="82"/>
+      <c r="CM20" s="82"/>
+      <c r="CN20" s="82"/>
+      <c r="CO20" s="82"/>
+      <c r="CP20" s="82"/>
+      <c r="CQ20" s="82"/>
+      <c r="CR20" s="82"/>
+      <c r="CS20" s="82"/>
+      <c r="CT20" s="82"/>
+      <c r="CU20" s="82"/>
+      <c r="CV20" s="82"/>
+      <c r="CW20" s="82"/>
+      <c r="CX20" s="82"/>
+      <c r="CY20" s="82"/>
+      <c r="CZ20" s="82"/>
     </row>
     <row r="21" spans="1:104" ht="35.25" customHeight="1">
       <c r="A21"/>
@@ -2386,16 +2415,16 @@
         <v>16</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G21" s="38">
         <v>24</v>
@@ -2403,7 +2432,7 @@
       <c r="H21" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="82">
+      <c r="I21" s="81">
         <v>1</v>
       </c>
       <c r="J21" s="18"/>
@@ -2423,86 +2452,86 @@
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
       <c r="X21" s="9"/>
-      <c r="Y21" s="81"/>
-      <c r="Z21" s="81"/>
-      <c r="AA21" s="81"/>
-      <c r="AB21" s="81"/>
-      <c r="AC21" s="81"/>
-      <c r="AD21" s="81"/>
-      <c r="AE21" s="81"/>
-      <c r="AF21" s="81"/>
-      <c r="AG21" s="81"/>
-      <c r="AH21" s="81"/>
-      <c r="AI21" s="81"/>
-      <c r="AJ21" s="81"/>
-      <c r="AK21" s="81"/>
-      <c r="AL21" s="81"/>
-      <c r="AM21" s="81"/>
-      <c r="AN21" s="81"/>
-      <c r="AO21" s="81"/>
-      <c r="AP21" s="81"/>
-      <c r="AQ21" s="81"/>
-      <c r="AR21" s="81"/>
-      <c r="AS21" s="81"/>
-      <c r="AT21" s="81"/>
-      <c r="AU21" s="81"/>
-      <c r="AV21" s="81"/>
-      <c r="AW21" s="81"/>
-      <c r="AX21" s="81"/>
-      <c r="AY21" s="81"/>
-      <c r="AZ21" s="81"/>
-      <c r="BA21" s="81"/>
-      <c r="BB21" s="81"/>
-      <c r="BC21" s="81"/>
-      <c r="BD21" s="81"/>
-      <c r="BE21" s="81"/>
-      <c r="BF21" s="81"/>
-      <c r="BG21" s="81"/>
-      <c r="BH21" s="81"/>
-      <c r="BI21" s="81"/>
-      <c r="BJ21" s="81"/>
-      <c r="BK21" s="81"/>
-      <c r="BL21" s="81"/>
-      <c r="BM21" s="81"/>
-      <c r="BN21" s="81"/>
-      <c r="BO21" s="81"/>
-      <c r="BP21" s="81"/>
-      <c r="BQ21" s="81"/>
-      <c r="BR21" s="81"/>
-      <c r="BS21" s="81"/>
-      <c r="BT21" s="81"/>
-      <c r="BU21" s="81"/>
-      <c r="BV21" s="81"/>
-      <c r="BW21" s="81"/>
-      <c r="BX21" s="81"/>
-      <c r="BY21" s="81"/>
-      <c r="BZ21" s="81"/>
-      <c r="CA21" s="81"/>
-      <c r="CB21" s="81"/>
-      <c r="CC21" s="81"/>
-      <c r="CD21" s="81"/>
-      <c r="CE21" s="81"/>
-      <c r="CF21" s="81"/>
-      <c r="CG21" s="81"/>
-      <c r="CH21" s="81"/>
-      <c r="CI21" s="81"/>
-      <c r="CJ21" s="81"/>
-      <c r="CK21" s="81"/>
-      <c r="CL21" s="81"/>
-      <c r="CM21" s="81"/>
-      <c r="CN21" s="81"/>
-      <c r="CO21" s="81"/>
-      <c r="CP21" s="81"/>
-      <c r="CQ21" s="81"/>
-      <c r="CR21" s="81"/>
-      <c r="CS21" s="81"/>
-      <c r="CT21" s="81"/>
-      <c r="CU21" s="81"/>
-      <c r="CV21" s="81"/>
-      <c r="CW21" s="81"/>
-      <c r="CX21" s="81"/>
-      <c r="CY21" s="81"/>
-      <c r="CZ21" s="81"/>
+      <c r="Y21" s="82"/>
+      <c r="Z21" s="82"/>
+      <c r="AA21" s="82"/>
+      <c r="AB21" s="82"/>
+      <c r="AC21" s="82"/>
+      <c r="AD21" s="82"/>
+      <c r="AE21" s="82"/>
+      <c r="AF21" s="82"/>
+      <c r="AG21" s="82"/>
+      <c r="AH21" s="82"/>
+      <c r="AI21" s="82"/>
+      <c r="AJ21" s="82"/>
+      <c r="AK21" s="82"/>
+      <c r="AL21" s="82"/>
+      <c r="AM21" s="82"/>
+      <c r="AN21" s="82"/>
+      <c r="AO21" s="82"/>
+      <c r="AP21" s="82"/>
+      <c r="AQ21" s="82"/>
+      <c r="AR21" s="82"/>
+      <c r="AS21" s="82"/>
+      <c r="AT21" s="82"/>
+      <c r="AU21" s="82"/>
+      <c r="AV21" s="82"/>
+      <c r="AW21" s="82"/>
+      <c r="AX21" s="82"/>
+      <c r="AY21" s="82"/>
+      <c r="AZ21" s="82"/>
+      <c r="BA21" s="82"/>
+      <c r="BB21" s="82"/>
+      <c r="BC21" s="82"/>
+      <c r="BD21" s="82"/>
+      <c r="BE21" s="82"/>
+      <c r="BF21" s="82"/>
+      <c r="BG21" s="82"/>
+      <c r="BH21" s="82"/>
+      <c r="BI21" s="82"/>
+      <c r="BJ21" s="82"/>
+      <c r="BK21" s="82"/>
+      <c r="BL21" s="82"/>
+      <c r="BM21" s="82"/>
+      <c r="BN21" s="82"/>
+      <c r="BO21" s="82"/>
+      <c r="BP21" s="82"/>
+      <c r="BQ21" s="82"/>
+      <c r="BR21" s="82"/>
+      <c r="BS21" s="82"/>
+      <c r="BT21" s="82"/>
+      <c r="BU21" s="82"/>
+      <c r="BV21" s="82"/>
+      <c r="BW21" s="82"/>
+      <c r="BX21" s="82"/>
+      <c r="BY21" s="82"/>
+      <c r="BZ21" s="82"/>
+      <c r="CA21" s="82"/>
+      <c r="CB21" s="82"/>
+      <c r="CC21" s="82"/>
+      <c r="CD21" s="82"/>
+      <c r="CE21" s="82"/>
+      <c r="CF21" s="82"/>
+      <c r="CG21" s="82"/>
+      <c r="CH21" s="82"/>
+      <c r="CI21" s="82"/>
+      <c r="CJ21" s="82"/>
+      <c r="CK21" s="82"/>
+      <c r="CL21" s="82"/>
+      <c r="CM21" s="82"/>
+      <c r="CN21" s="82"/>
+      <c r="CO21" s="82"/>
+      <c r="CP21" s="82"/>
+      <c r="CQ21" s="82"/>
+      <c r="CR21" s="82"/>
+      <c r="CS21" s="82"/>
+      <c r="CT21" s="82"/>
+      <c r="CU21" s="82"/>
+      <c r="CV21" s="82"/>
+      <c r="CW21" s="82"/>
+      <c r="CX21" s="82"/>
+      <c r="CY21" s="82"/>
+      <c r="CZ21" s="82"/>
     </row>
     <row r="22" spans="1:104" ht="35.25" customHeight="1">
       <c r="A22"/>
@@ -2510,22 +2539,22 @@
         <v>17</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E22" s="48" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F22" s="48" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G22" s="38">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I22" s="73">
         <v>0.6</v>
@@ -2545,86 +2574,86 @@
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
-      <c r="Y22" s="81"/>
-      <c r="Z22" s="81"/>
-      <c r="AA22" s="81"/>
-      <c r="AB22" s="81"/>
-      <c r="AC22" s="81"/>
-      <c r="AD22" s="81"/>
-      <c r="AE22" s="81"/>
-      <c r="AF22" s="81"/>
-      <c r="AG22" s="81"/>
-      <c r="AH22" s="81"/>
-      <c r="AI22" s="81"/>
-      <c r="AJ22" s="81"/>
-      <c r="AK22" s="81"/>
-      <c r="AL22" s="81"/>
-      <c r="AM22" s="81"/>
-      <c r="AN22" s="81"/>
-      <c r="AO22" s="81"/>
-      <c r="AP22" s="81"/>
-      <c r="AQ22" s="81"/>
-      <c r="AR22" s="81"/>
-      <c r="AS22" s="81"/>
-      <c r="AT22" s="81"/>
-      <c r="AU22" s="81"/>
-      <c r="AV22" s="81"/>
-      <c r="AW22" s="81"/>
-      <c r="AX22" s="81"/>
-      <c r="AY22" s="81"/>
-      <c r="AZ22" s="81"/>
-      <c r="BA22" s="81"/>
-      <c r="BB22" s="81"/>
-      <c r="BC22" s="81"/>
-      <c r="BD22" s="81"/>
-      <c r="BE22" s="81"/>
-      <c r="BF22" s="81"/>
-      <c r="BG22" s="81"/>
-      <c r="BH22" s="81"/>
-      <c r="BI22" s="81"/>
-      <c r="BJ22" s="81"/>
-      <c r="BK22" s="81"/>
-      <c r="BL22" s="81"/>
-      <c r="BM22" s="81"/>
-      <c r="BN22" s="81"/>
-      <c r="BO22" s="81"/>
-      <c r="BP22" s="81"/>
-      <c r="BQ22" s="81"/>
-      <c r="BR22" s="81"/>
-      <c r="BS22" s="81"/>
-      <c r="BT22" s="81"/>
-      <c r="BU22" s="81"/>
-      <c r="BV22" s="81"/>
-      <c r="BW22" s="81"/>
-      <c r="BX22" s="81"/>
-      <c r="BY22" s="81"/>
-      <c r="BZ22" s="81"/>
-      <c r="CA22" s="81"/>
-      <c r="CB22" s="81"/>
-      <c r="CC22" s="81"/>
-      <c r="CD22" s="81"/>
-      <c r="CE22" s="81"/>
-      <c r="CF22" s="81"/>
-      <c r="CG22" s="81"/>
-      <c r="CH22" s="81"/>
-      <c r="CI22" s="81"/>
-      <c r="CJ22" s="81"/>
-      <c r="CK22" s="81"/>
-      <c r="CL22" s="81"/>
-      <c r="CM22" s="81"/>
-      <c r="CN22" s="81"/>
-      <c r="CO22" s="81"/>
-      <c r="CP22" s="81"/>
-      <c r="CQ22" s="81"/>
-      <c r="CR22" s="81"/>
-      <c r="CS22" s="81"/>
-      <c r="CT22" s="81"/>
-      <c r="CU22" s="81"/>
-      <c r="CV22" s="81"/>
-      <c r="CW22" s="81"/>
-      <c r="CX22" s="81"/>
-      <c r="CY22" s="81"/>
-      <c r="CZ22" s="81"/>
+      <c r="Y22" s="82"/>
+      <c r="Z22" s="82"/>
+      <c r="AA22" s="82"/>
+      <c r="AB22" s="82"/>
+      <c r="AC22" s="82"/>
+      <c r="AD22" s="82"/>
+      <c r="AE22" s="82"/>
+      <c r="AF22" s="82"/>
+      <c r="AG22" s="82"/>
+      <c r="AH22" s="82"/>
+      <c r="AI22" s="82"/>
+      <c r="AJ22" s="82"/>
+      <c r="AK22" s="82"/>
+      <c r="AL22" s="82"/>
+      <c r="AM22" s="82"/>
+      <c r="AN22" s="82"/>
+      <c r="AO22" s="82"/>
+      <c r="AP22" s="82"/>
+      <c r="AQ22" s="82"/>
+      <c r="AR22" s="82"/>
+      <c r="AS22" s="82"/>
+      <c r="AT22" s="82"/>
+      <c r="AU22" s="82"/>
+      <c r="AV22" s="82"/>
+      <c r="AW22" s="82"/>
+      <c r="AX22" s="82"/>
+      <c r="AY22" s="82"/>
+      <c r="AZ22" s="82"/>
+      <c r="BA22" s="82"/>
+      <c r="BB22" s="82"/>
+      <c r="BC22" s="82"/>
+      <c r="BD22" s="82"/>
+      <c r="BE22" s="82"/>
+      <c r="BF22" s="82"/>
+      <c r="BG22" s="82"/>
+      <c r="BH22" s="82"/>
+      <c r="BI22" s="82"/>
+      <c r="BJ22" s="82"/>
+      <c r="BK22" s="82"/>
+      <c r="BL22" s="82"/>
+      <c r="BM22" s="82"/>
+      <c r="BN22" s="82"/>
+      <c r="BO22" s="82"/>
+      <c r="BP22" s="82"/>
+      <c r="BQ22" s="82"/>
+      <c r="BR22" s="82"/>
+      <c r="BS22" s="82"/>
+      <c r="BT22" s="82"/>
+      <c r="BU22" s="82"/>
+      <c r="BV22" s="82"/>
+      <c r="BW22" s="82"/>
+      <c r="BX22" s="82"/>
+      <c r="BY22" s="82"/>
+      <c r="BZ22" s="82"/>
+      <c r="CA22" s="82"/>
+      <c r="CB22" s="82"/>
+      <c r="CC22" s="82"/>
+      <c r="CD22" s="82"/>
+      <c r="CE22" s="82"/>
+      <c r="CF22" s="82"/>
+      <c r="CG22" s="82"/>
+      <c r="CH22" s="82"/>
+      <c r="CI22" s="82"/>
+      <c r="CJ22" s="82"/>
+      <c r="CK22" s="82"/>
+      <c r="CL22" s="82"/>
+      <c r="CM22" s="82"/>
+      <c r="CN22" s="82"/>
+      <c r="CO22" s="82"/>
+      <c r="CP22" s="82"/>
+      <c r="CQ22" s="82"/>
+      <c r="CR22" s="82"/>
+      <c r="CS22" s="82"/>
+      <c r="CT22" s="82"/>
+      <c r="CU22" s="82"/>
+      <c r="CV22" s="82"/>
+      <c r="CW22" s="82"/>
+      <c r="CX22" s="82"/>
+      <c r="CY22" s="82"/>
+      <c r="CZ22" s="82"/>
     </row>
     <row r="23" spans="1:104" ht="35.25" customHeight="1">
       <c r="A23"/>
@@ -2632,23 +2661,25 @@
         <v>18</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E23" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="F23" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="G23" s="47"/>
+      <c r="G23" s="47">
+        <v>23</v>
+      </c>
       <c r="H23" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="I23" s="53">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="I23" s="81">
+        <v>0.6</v>
       </c>
       <c r="J23" s="18"/>
       <c r="K23" s="9"/>
@@ -2665,86 +2696,86 @@
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
-      <c r="Y23" s="81"/>
-      <c r="Z23" s="81"/>
-      <c r="AA23" s="81"/>
-      <c r="AB23" s="81"/>
-      <c r="AC23" s="81"/>
-      <c r="AD23" s="81"/>
-      <c r="AE23" s="81"/>
-      <c r="AF23" s="81"/>
-      <c r="AG23" s="81"/>
-      <c r="AH23" s="81"/>
-      <c r="AI23" s="81"/>
-      <c r="AJ23" s="81"/>
-      <c r="AK23" s="81"/>
-      <c r="AL23" s="81"/>
-      <c r="AM23" s="81"/>
-      <c r="AN23" s="81"/>
-      <c r="AO23" s="81"/>
-      <c r="AP23" s="81"/>
-      <c r="AQ23" s="81"/>
-      <c r="AR23" s="81"/>
-      <c r="AS23" s="81"/>
-      <c r="AT23" s="81"/>
-      <c r="AU23" s="81"/>
-      <c r="AV23" s="81"/>
-      <c r="AW23" s="81"/>
-      <c r="AX23" s="81"/>
-      <c r="AY23" s="81"/>
-      <c r="AZ23" s="81"/>
-      <c r="BA23" s="81"/>
-      <c r="BB23" s="81"/>
-      <c r="BC23" s="81"/>
-      <c r="BD23" s="81"/>
-      <c r="BE23" s="81"/>
-      <c r="BF23" s="81"/>
-      <c r="BG23" s="81"/>
-      <c r="BH23" s="81"/>
-      <c r="BI23" s="81"/>
-      <c r="BJ23" s="81"/>
-      <c r="BK23" s="81"/>
-      <c r="BL23" s="81"/>
-      <c r="BM23" s="81"/>
-      <c r="BN23" s="81"/>
-      <c r="BO23" s="81"/>
-      <c r="BP23" s="81"/>
-      <c r="BQ23" s="81"/>
-      <c r="BR23" s="81"/>
-      <c r="BS23" s="81"/>
-      <c r="BT23" s="81"/>
-      <c r="BU23" s="81"/>
-      <c r="BV23" s="81"/>
-      <c r="BW23" s="81"/>
-      <c r="BX23" s="81"/>
-      <c r="BY23" s="81"/>
-      <c r="BZ23" s="81"/>
-      <c r="CA23" s="81"/>
-      <c r="CB23" s="81"/>
-      <c r="CC23" s="81"/>
-      <c r="CD23" s="81"/>
-      <c r="CE23" s="81"/>
-      <c r="CF23" s="81"/>
-      <c r="CG23" s="81"/>
-      <c r="CH23" s="81"/>
-      <c r="CI23" s="81"/>
-      <c r="CJ23" s="81"/>
-      <c r="CK23" s="81"/>
-      <c r="CL23" s="81"/>
-      <c r="CM23" s="81"/>
-      <c r="CN23" s="81"/>
-      <c r="CO23" s="81"/>
-      <c r="CP23" s="81"/>
-      <c r="CQ23" s="81"/>
-      <c r="CR23" s="81"/>
-      <c r="CS23" s="81"/>
-      <c r="CT23" s="81"/>
-      <c r="CU23" s="81"/>
-      <c r="CV23" s="81"/>
-      <c r="CW23" s="81"/>
-      <c r="CX23" s="81"/>
-      <c r="CY23" s="81"/>
-      <c r="CZ23" s="81"/>
+      <c r="Y23" s="82"/>
+      <c r="Z23" s="82"/>
+      <c r="AA23" s="82"/>
+      <c r="AB23" s="82"/>
+      <c r="AC23" s="82"/>
+      <c r="AD23" s="82"/>
+      <c r="AE23" s="82"/>
+      <c r="AF23" s="82"/>
+      <c r="AG23" s="82"/>
+      <c r="AH23" s="82"/>
+      <c r="AI23" s="82"/>
+      <c r="AJ23" s="82"/>
+      <c r="AK23" s="82"/>
+      <c r="AL23" s="82"/>
+      <c r="AM23" s="82"/>
+      <c r="AN23" s="82"/>
+      <c r="AO23" s="82"/>
+      <c r="AP23" s="82"/>
+      <c r="AQ23" s="82"/>
+      <c r="AR23" s="82"/>
+      <c r="AS23" s="82"/>
+      <c r="AT23" s="82"/>
+      <c r="AU23" s="82"/>
+      <c r="AV23" s="82"/>
+      <c r="AW23" s="82"/>
+      <c r="AX23" s="82"/>
+      <c r="AY23" s="82"/>
+      <c r="AZ23" s="82"/>
+      <c r="BA23" s="82"/>
+      <c r="BB23" s="82"/>
+      <c r="BC23" s="82"/>
+      <c r="BD23" s="82"/>
+      <c r="BE23" s="82"/>
+      <c r="BF23" s="82"/>
+      <c r="BG23" s="82"/>
+      <c r="BH23" s="82"/>
+      <c r="BI23" s="82"/>
+      <c r="BJ23" s="82"/>
+      <c r="BK23" s="82"/>
+      <c r="BL23" s="82"/>
+      <c r="BM23" s="82"/>
+      <c r="BN23" s="82"/>
+      <c r="BO23" s="82"/>
+      <c r="BP23" s="82"/>
+      <c r="BQ23" s="82"/>
+      <c r="BR23" s="82"/>
+      <c r="BS23" s="82"/>
+      <c r="BT23" s="82"/>
+      <c r="BU23" s="82"/>
+      <c r="BV23" s="82"/>
+      <c r="BW23" s="82"/>
+      <c r="BX23" s="82"/>
+      <c r="BY23" s="82"/>
+      <c r="BZ23" s="82"/>
+      <c r="CA23" s="82"/>
+      <c r="CB23" s="82"/>
+      <c r="CC23" s="82"/>
+      <c r="CD23" s="82"/>
+      <c r="CE23" s="82"/>
+      <c r="CF23" s="82"/>
+      <c r="CG23" s="82"/>
+      <c r="CH23" s="82"/>
+      <c r="CI23" s="82"/>
+      <c r="CJ23" s="82"/>
+      <c r="CK23" s="82"/>
+      <c r="CL23" s="82"/>
+      <c r="CM23" s="82"/>
+      <c r="CN23" s="82"/>
+      <c r="CO23" s="82"/>
+      <c r="CP23" s="82"/>
+      <c r="CQ23" s="82"/>
+      <c r="CR23" s="82"/>
+      <c r="CS23" s="82"/>
+      <c r="CT23" s="82"/>
+      <c r="CU23" s="82"/>
+      <c r="CV23" s="82"/>
+      <c r="CW23" s="82"/>
+      <c r="CX23" s="82"/>
+      <c r="CY23" s="82"/>
+      <c r="CZ23" s="82"/>
     </row>
     <row r="24" spans="1:104" s="30" customFormat="1" ht="35.25" customHeight="1">
       <c r="A24"/>
@@ -2752,20 +2783,20 @@
         <v>19</v>
       </c>
       <c r="C24" s="62" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D24" s="55" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E24" s="63" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F24" s="63" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G24" s="47"/>
       <c r="H24" s="54" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I24" s="55">
         <v>0</v>
@@ -2785,86 +2816,86 @@
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
       <c r="X24" s="9"/>
-      <c r="Y24" s="81"/>
-      <c r="Z24" s="81"/>
-      <c r="AA24" s="81"/>
-      <c r="AB24" s="81"/>
-      <c r="AC24" s="81"/>
-      <c r="AD24" s="81"/>
-      <c r="AE24" s="81"/>
-      <c r="AF24" s="81"/>
-      <c r="AG24" s="81"/>
-      <c r="AH24" s="81"/>
-      <c r="AI24" s="81"/>
-      <c r="AJ24" s="81"/>
-      <c r="AK24" s="81"/>
-      <c r="AL24" s="81"/>
-      <c r="AM24" s="81"/>
-      <c r="AN24" s="81"/>
-      <c r="AO24" s="81"/>
-      <c r="AP24" s="81"/>
-      <c r="AQ24" s="81"/>
-      <c r="AR24" s="81"/>
-      <c r="AS24" s="81"/>
-      <c r="AT24" s="81"/>
-      <c r="AU24" s="81"/>
-      <c r="AV24" s="81"/>
-      <c r="AW24" s="81"/>
-      <c r="AX24" s="81"/>
-      <c r="AY24" s="81"/>
-      <c r="AZ24" s="81"/>
-      <c r="BA24" s="81"/>
-      <c r="BB24" s="81"/>
-      <c r="BC24" s="81"/>
-      <c r="BD24" s="81"/>
-      <c r="BE24" s="81"/>
-      <c r="BF24" s="81"/>
-      <c r="BG24" s="81"/>
-      <c r="BH24" s="81"/>
-      <c r="BI24" s="81"/>
-      <c r="BJ24" s="81"/>
-      <c r="BK24" s="81"/>
-      <c r="BL24" s="81"/>
-      <c r="BM24" s="81"/>
-      <c r="BN24" s="81"/>
-      <c r="BO24" s="81"/>
-      <c r="BP24" s="81"/>
-      <c r="BQ24" s="81"/>
-      <c r="BR24" s="81"/>
-      <c r="BS24" s="81"/>
-      <c r="BT24" s="81"/>
-      <c r="BU24" s="81"/>
-      <c r="BV24" s="81"/>
-      <c r="BW24" s="81"/>
-      <c r="BX24" s="81"/>
-      <c r="BY24" s="81"/>
-      <c r="BZ24" s="81"/>
-      <c r="CA24" s="81"/>
-      <c r="CB24" s="81"/>
-      <c r="CC24" s="81"/>
-      <c r="CD24" s="81"/>
-      <c r="CE24" s="81"/>
-      <c r="CF24" s="81"/>
-      <c r="CG24" s="81"/>
-      <c r="CH24" s="81"/>
-      <c r="CI24" s="81"/>
-      <c r="CJ24" s="81"/>
-      <c r="CK24" s="81"/>
-      <c r="CL24" s="81"/>
-      <c r="CM24" s="81"/>
-      <c r="CN24" s="81"/>
-      <c r="CO24" s="81"/>
-      <c r="CP24" s="81"/>
-      <c r="CQ24" s="81"/>
-      <c r="CR24" s="81"/>
-      <c r="CS24" s="81"/>
-      <c r="CT24" s="81"/>
-      <c r="CU24" s="81"/>
-      <c r="CV24" s="81"/>
-      <c r="CW24" s="81"/>
-      <c r="CX24" s="81"/>
-      <c r="CY24" s="81"/>
-      <c r="CZ24" s="81"/>
+      <c r="Y24" s="82"/>
+      <c r="Z24" s="82"/>
+      <c r="AA24" s="82"/>
+      <c r="AB24" s="82"/>
+      <c r="AC24" s="82"/>
+      <c r="AD24" s="82"/>
+      <c r="AE24" s="82"/>
+      <c r="AF24" s="82"/>
+      <c r="AG24" s="82"/>
+      <c r="AH24" s="82"/>
+      <c r="AI24" s="82"/>
+      <c r="AJ24" s="82"/>
+      <c r="AK24" s="82"/>
+      <c r="AL24" s="82"/>
+      <c r="AM24" s="82"/>
+      <c r="AN24" s="82"/>
+      <c r="AO24" s="82"/>
+      <c r="AP24" s="82"/>
+      <c r="AQ24" s="82"/>
+      <c r="AR24" s="82"/>
+      <c r="AS24" s="82"/>
+      <c r="AT24" s="82"/>
+      <c r="AU24" s="82"/>
+      <c r="AV24" s="82"/>
+      <c r="AW24" s="82"/>
+      <c r="AX24" s="82"/>
+      <c r="AY24" s="82"/>
+      <c r="AZ24" s="82"/>
+      <c r="BA24" s="82"/>
+      <c r="BB24" s="82"/>
+      <c r="BC24" s="82"/>
+      <c r="BD24" s="82"/>
+      <c r="BE24" s="82"/>
+      <c r="BF24" s="82"/>
+      <c r="BG24" s="82"/>
+      <c r="BH24" s="82"/>
+      <c r="BI24" s="82"/>
+      <c r="BJ24" s="82"/>
+      <c r="BK24" s="82"/>
+      <c r="BL24" s="82"/>
+      <c r="BM24" s="82"/>
+      <c r="BN24" s="82"/>
+      <c r="BO24" s="82"/>
+      <c r="BP24" s="82"/>
+      <c r="BQ24" s="82"/>
+      <c r="BR24" s="82"/>
+      <c r="BS24" s="82"/>
+      <c r="BT24" s="82"/>
+      <c r="BU24" s="82"/>
+      <c r="BV24" s="82"/>
+      <c r="BW24" s="82"/>
+      <c r="BX24" s="82"/>
+      <c r="BY24" s="82"/>
+      <c r="BZ24" s="82"/>
+      <c r="CA24" s="82"/>
+      <c r="CB24" s="82"/>
+      <c r="CC24" s="82"/>
+      <c r="CD24" s="82"/>
+      <c r="CE24" s="82"/>
+      <c r="CF24" s="82"/>
+      <c r="CG24" s="82"/>
+      <c r="CH24" s="82"/>
+      <c r="CI24" s="82"/>
+      <c r="CJ24" s="82"/>
+      <c r="CK24" s="82"/>
+      <c r="CL24" s="82"/>
+      <c r="CM24" s="82"/>
+      <c r="CN24" s="82"/>
+      <c r="CO24" s="82"/>
+      <c r="CP24" s="82"/>
+      <c r="CQ24" s="82"/>
+      <c r="CR24" s="82"/>
+      <c r="CS24" s="82"/>
+      <c r="CT24" s="82"/>
+      <c r="CU24" s="82"/>
+      <c r="CV24" s="82"/>
+      <c r="CW24" s="82"/>
+      <c r="CX24" s="82"/>
+      <c r="CY24" s="82"/>
+      <c r="CZ24" s="82"/>
     </row>
     <row r="25" spans="1:104" s="30" customFormat="1" ht="35.25" customHeight="1">
       <c r="A25" s="46"/>
@@ -2872,22 +2903,22 @@
         <v>20</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G25" s="38">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H25" s="53" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I25" s="74">
         <v>0.8</v>
@@ -2907,86 +2938,86 @@
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
       <c r="X25" s="9"/>
-      <c r="Y25" s="81"/>
-      <c r="Z25" s="81"/>
-      <c r="AA25" s="81"/>
-      <c r="AB25" s="81"/>
-      <c r="AC25" s="81"/>
-      <c r="AD25" s="81"/>
-      <c r="AE25" s="81"/>
-      <c r="AF25" s="81"/>
-      <c r="AG25" s="81"/>
-      <c r="AH25" s="81"/>
-      <c r="AI25" s="81"/>
-      <c r="AJ25" s="81"/>
-      <c r="AK25" s="81"/>
-      <c r="AL25" s="81"/>
-      <c r="AM25" s="81"/>
-      <c r="AN25" s="81"/>
-      <c r="AO25" s="81"/>
-      <c r="AP25" s="81"/>
-      <c r="AQ25" s="81"/>
-      <c r="AR25" s="81"/>
-      <c r="AS25" s="81"/>
-      <c r="AT25" s="81"/>
-      <c r="AU25" s="81"/>
-      <c r="AV25" s="81"/>
-      <c r="AW25" s="81"/>
-      <c r="AX25" s="81"/>
-      <c r="AY25" s="81"/>
-      <c r="AZ25" s="81"/>
-      <c r="BA25" s="81"/>
-      <c r="BB25" s="81"/>
-      <c r="BC25" s="81"/>
-      <c r="BD25" s="81"/>
-      <c r="BE25" s="81"/>
-      <c r="BF25" s="81"/>
-      <c r="BG25" s="81"/>
-      <c r="BH25" s="81"/>
-      <c r="BI25" s="81"/>
-      <c r="BJ25" s="81"/>
-      <c r="BK25" s="81"/>
-      <c r="BL25" s="81"/>
-      <c r="BM25" s="81"/>
-      <c r="BN25" s="81"/>
-      <c r="BO25" s="81"/>
-      <c r="BP25" s="81"/>
-      <c r="BQ25" s="81"/>
-      <c r="BR25" s="81"/>
-      <c r="BS25" s="81"/>
-      <c r="BT25" s="81"/>
-      <c r="BU25" s="81"/>
-      <c r="BV25" s="81"/>
-      <c r="BW25" s="81"/>
-      <c r="BX25" s="81"/>
-      <c r="BY25" s="81"/>
-      <c r="BZ25" s="81"/>
-      <c r="CA25" s="81"/>
-      <c r="CB25" s="81"/>
-      <c r="CC25" s="81"/>
-      <c r="CD25" s="81"/>
-      <c r="CE25" s="81"/>
-      <c r="CF25" s="81"/>
-      <c r="CG25" s="81"/>
-      <c r="CH25" s="81"/>
-      <c r="CI25" s="81"/>
-      <c r="CJ25" s="81"/>
-      <c r="CK25" s="81"/>
-      <c r="CL25" s="81"/>
-      <c r="CM25" s="81"/>
-      <c r="CN25" s="81"/>
-      <c r="CO25" s="81"/>
-      <c r="CP25" s="81"/>
-      <c r="CQ25" s="81"/>
-      <c r="CR25" s="81"/>
-      <c r="CS25" s="81"/>
-      <c r="CT25" s="81"/>
-      <c r="CU25" s="81"/>
-      <c r="CV25" s="81"/>
-      <c r="CW25" s="81"/>
-      <c r="CX25" s="81"/>
-      <c r="CY25" s="81"/>
-      <c r="CZ25" s="81"/>
+      <c r="Y25" s="82"/>
+      <c r="Z25" s="82"/>
+      <c r="AA25" s="82"/>
+      <c r="AB25" s="82"/>
+      <c r="AC25" s="82"/>
+      <c r="AD25" s="82"/>
+      <c r="AE25" s="82"/>
+      <c r="AF25" s="82"/>
+      <c r="AG25" s="82"/>
+      <c r="AH25" s="82"/>
+      <c r="AI25" s="82"/>
+      <c r="AJ25" s="82"/>
+      <c r="AK25" s="82"/>
+      <c r="AL25" s="82"/>
+      <c r="AM25" s="82"/>
+      <c r="AN25" s="82"/>
+      <c r="AO25" s="82"/>
+      <c r="AP25" s="82"/>
+      <c r="AQ25" s="82"/>
+      <c r="AR25" s="82"/>
+      <c r="AS25" s="82"/>
+      <c r="AT25" s="82"/>
+      <c r="AU25" s="82"/>
+      <c r="AV25" s="82"/>
+      <c r="AW25" s="82"/>
+      <c r="AX25" s="82"/>
+      <c r="AY25" s="82"/>
+      <c r="AZ25" s="82"/>
+      <c r="BA25" s="82"/>
+      <c r="BB25" s="82"/>
+      <c r="BC25" s="82"/>
+      <c r="BD25" s="82"/>
+      <c r="BE25" s="82"/>
+      <c r="BF25" s="82"/>
+      <c r="BG25" s="82"/>
+      <c r="BH25" s="82"/>
+      <c r="BI25" s="82"/>
+      <c r="BJ25" s="82"/>
+      <c r="BK25" s="82"/>
+      <c r="BL25" s="82"/>
+      <c r="BM25" s="82"/>
+      <c r="BN25" s="82"/>
+      <c r="BO25" s="82"/>
+      <c r="BP25" s="82"/>
+      <c r="BQ25" s="82"/>
+      <c r="BR25" s="82"/>
+      <c r="BS25" s="82"/>
+      <c r="BT25" s="82"/>
+      <c r="BU25" s="82"/>
+      <c r="BV25" s="82"/>
+      <c r="BW25" s="82"/>
+      <c r="BX25" s="82"/>
+      <c r="BY25" s="82"/>
+      <c r="BZ25" s="82"/>
+      <c r="CA25" s="82"/>
+      <c r="CB25" s="82"/>
+      <c r="CC25" s="82"/>
+      <c r="CD25" s="82"/>
+      <c r="CE25" s="82"/>
+      <c r="CF25" s="82"/>
+      <c r="CG25" s="82"/>
+      <c r="CH25" s="82"/>
+      <c r="CI25" s="82"/>
+      <c r="CJ25" s="82"/>
+      <c r="CK25" s="82"/>
+      <c r="CL25" s="82"/>
+      <c r="CM25" s="82"/>
+      <c r="CN25" s="82"/>
+      <c r="CO25" s="82"/>
+      <c r="CP25" s="82"/>
+      <c r="CQ25" s="82"/>
+      <c r="CR25" s="82"/>
+      <c r="CS25" s="82"/>
+      <c r="CT25" s="82"/>
+      <c r="CU25" s="82"/>
+      <c r="CV25" s="82"/>
+      <c r="CW25" s="82"/>
+      <c r="CX25" s="82"/>
+      <c r="CY25" s="82"/>
+      <c r="CZ25" s="82"/>
     </row>
     <row r="26" spans="1:104" s="30" customFormat="1" ht="35.25" customHeight="1">
       <c r="A26" s="46"/>
@@ -2994,20 +3025,20 @@
         <v>21</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D26" s="57" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F26" s="35" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="55" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I26" s="55">
         <v>0</v>
@@ -3027,86 +3058,86 @@
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
-      <c r="Y26" s="81"/>
-      <c r="Z26" s="81"/>
-      <c r="AA26" s="81"/>
-      <c r="AB26" s="81"/>
-      <c r="AC26" s="81"/>
-      <c r="AD26" s="81"/>
-      <c r="AE26" s="81"/>
-      <c r="AF26" s="81"/>
-      <c r="AG26" s="81"/>
-      <c r="AH26" s="81"/>
-      <c r="AI26" s="81"/>
-      <c r="AJ26" s="81"/>
-      <c r="AK26" s="81"/>
-      <c r="AL26" s="81"/>
-      <c r="AM26" s="81"/>
-      <c r="AN26" s="81"/>
-      <c r="AO26" s="81"/>
-      <c r="AP26" s="81"/>
-      <c r="AQ26" s="81"/>
-      <c r="AR26" s="81"/>
-      <c r="AS26" s="81"/>
-      <c r="AT26" s="81"/>
-      <c r="AU26" s="81"/>
-      <c r="AV26" s="81"/>
-      <c r="AW26" s="81"/>
-      <c r="AX26" s="81"/>
-      <c r="AY26" s="81"/>
-      <c r="AZ26" s="81"/>
-      <c r="BA26" s="81"/>
-      <c r="BB26" s="81"/>
-      <c r="BC26" s="81"/>
-      <c r="BD26" s="81"/>
-      <c r="BE26" s="81"/>
-      <c r="BF26" s="81"/>
-      <c r="BG26" s="81"/>
-      <c r="BH26" s="81"/>
-      <c r="BI26" s="81"/>
-      <c r="BJ26" s="81"/>
-      <c r="BK26" s="81"/>
-      <c r="BL26" s="81"/>
-      <c r="BM26" s="81"/>
-      <c r="BN26" s="81"/>
-      <c r="BO26" s="81"/>
-      <c r="BP26" s="81"/>
-      <c r="BQ26" s="81"/>
-      <c r="BR26" s="81"/>
-      <c r="BS26" s="81"/>
-      <c r="BT26" s="81"/>
-      <c r="BU26" s="81"/>
-      <c r="BV26" s="81"/>
-      <c r="BW26" s="81"/>
-      <c r="BX26" s="81"/>
-      <c r="BY26" s="81"/>
-      <c r="BZ26" s="81"/>
-      <c r="CA26" s="81"/>
-      <c r="CB26" s="81"/>
-      <c r="CC26" s="81"/>
-      <c r="CD26" s="81"/>
-      <c r="CE26" s="81"/>
-      <c r="CF26" s="81"/>
-      <c r="CG26" s="81"/>
-      <c r="CH26" s="81"/>
-      <c r="CI26" s="81"/>
-      <c r="CJ26" s="81"/>
-      <c r="CK26" s="81"/>
-      <c r="CL26" s="81"/>
-      <c r="CM26" s="81"/>
-      <c r="CN26" s="81"/>
-      <c r="CO26" s="81"/>
-      <c r="CP26" s="81"/>
-      <c r="CQ26" s="81"/>
-      <c r="CR26" s="81"/>
-      <c r="CS26" s="81"/>
-      <c r="CT26" s="81"/>
-      <c r="CU26" s="81"/>
-      <c r="CV26" s="81"/>
-      <c r="CW26" s="81"/>
-      <c r="CX26" s="81"/>
-      <c r="CY26" s="81"/>
-      <c r="CZ26" s="81"/>
+      <c r="Y26" s="82"/>
+      <c r="Z26" s="82"/>
+      <c r="AA26" s="82"/>
+      <c r="AB26" s="82"/>
+      <c r="AC26" s="82"/>
+      <c r="AD26" s="82"/>
+      <c r="AE26" s="82"/>
+      <c r="AF26" s="82"/>
+      <c r="AG26" s="82"/>
+      <c r="AH26" s="82"/>
+      <c r="AI26" s="82"/>
+      <c r="AJ26" s="82"/>
+      <c r="AK26" s="82"/>
+      <c r="AL26" s="82"/>
+      <c r="AM26" s="82"/>
+      <c r="AN26" s="82"/>
+      <c r="AO26" s="82"/>
+      <c r="AP26" s="82"/>
+      <c r="AQ26" s="82"/>
+      <c r="AR26" s="82"/>
+      <c r="AS26" s="82"/>
+      <c r="AT26" s="82"/>
+      <c r="AU26" s="82"/>
+      <c r="AV26" s="82"/>
+      <c r="AW26" s="82"/>
+      <c r="AX26" s="82"/>
+      <c r="AY26" s="82"/>
+      <c r="AZ26" s="82"/>
+      <c r="BA26" s="82"/>
+      <c r="BB26" s="82"/>
+      <c r="BC26" s="82"/>
+      <c r="BD26" s="82"/>
+      <c r="BE26" s="82"/>
+      <c r="BF26" s="82"/>
+      <c r="BG26" s="82"/>
+      <c r="BH26" s="82"/>
+      <c r="BI26" s="82"/>
+      <c r="BJ26" s="82"/>
+      <c r="BK26" s="82"/>
+      <c r="BL26" s="82"/>
+      <c r="BM26" s="82"/>
+      <c r="BN26" s="82"/>
+      <c r="BO26" s="82"/>
+      <c r="BP26" s="82"/>
+      <c r="BQ26" s="82"/>
+      <c r="BR26" s="82"/>
+      <c r="BS26" s="82"/>
+      <c r="BT26" s="82"/>
+      <c r="BU26" s="82"/>
+      <c r="BV26" s="82"/>
+      <c r="BW26" s="82"/>
+      <c r="BX26" s="82"/>
+      <c r="BY26" s="82"/>
+      <c r="BZ26" s="82"/>
+      <c r="CA26" s="82"/>
+      <c r="CB26" s="82"/>
+      <c r="CC26" s="82"/>
+      <c r="CD26" s="82"/>
+      <c r="CE26" s="82"/>
+      <c r="CF26" s="82"/>
+      <c r="CG26" s="82"/>
+      <c r="CH26" s="82"/>
+      <c r="CI26" s="82"/>
+      <c r="CJ26" s="82"/>
+      <c r="CK26" s="82"/>
+      <c r="CL26" s="82"/>
+      <c r="CM26" s="82"/>
+      <c r="CN26" s="82"/>
+      <c r="CO26" s="82"/>
+      <c r="CP26" s="82"/>
+      <c r="CQ26" s="82"/>
+      <c r="CR26" s="82"/>
+      <c r="CS26" s="82"/>
+      <c r="CT26" s="82"/>
+      <c r="CU26" s="82"/>
+      <c r="CV26" s="82"/>
+      <c r="CW26" s="82"/>
+      <c r="CX26" s="82"/>
+      <c r="CY26" s="82"/>
+      <c r="CZ26" s="82"/>
     </row>
     <row r="27" spans="1:104" s="30" customFormat="1" ht="35.25" customHeight="1">
       <c r="A27" s="46"/>
@@ -3114,25 +3145,25 @@
         <v>22</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F27" s="45" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G27" s="38">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I27" s="74">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J27" s="18"/>
       <c r="K27" s="9"/>
@@ -3149,86 +3180,86 @@
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
-      <c r="Y27" s="81"/>
-      <c r="Z27" s="81"/>
-      <c r="AA27" s="81"/>
-      <c r="AB27" s="81"/>
-      <c r="AC27" s="81"/>
-      <c r="AD27" s="81"/>
-      <c r="AE27" s="81"/>
-      <c r="AF27" s="81"/>
-      <c r="AG27" s="81"/>
-      <c r="AH27" s="81"/>
-      <c r="AI27" s="81"/>
-      <c r="AJ27" s="81"/>
-      <c r="AK27" s="81"/>
-      <c r="AL27" s="81"/>
-      <c r="AM27" s="81"/>
-      <c r="AN27" s="81"/>
-      <c r="AO27" s="81"/>
-      <c r="AP27" s="81"/>
-      <c r="AQ27" s="81"/>
-      <c r="AR27" s="81"/>
-      <c r="AS27" s="81"/>
-      <c r="AT27" s="81"/>
-      <c r="AU27" s="81"/>
-      <c r="AV27" s="81"/>
-      <c r="AW27" s="81"/>
-      <c r="AX27" s="81"/>
-      <c r="AY27" s="81"/>
-      <c r="AZ27" s="81"/>
-      <c r="BA27" s="81"/>
-      <c r="BB27" s="81"/>
-      <c r="BC27" s="81"/>
-      <c r="BD27" s="81"/>
-      <c r="BE27" s="81"/>
-      <c r="BF27" s="81"/>
-      <c r="BG27" s="81"/>
-      <c r="BH27" s="81"/>
-      <c r="BI27" s="81"/>
-      <c r="BJ27" s="81"/>
-      <c r="BK27" s="81"/>
-      <c r="BL27" s="81"/>
-      <c r="BM27" s="81"/>
-      <c r="BN27" s="81"/>
-      <c r="BO27" s="81"/>
-      <c r="BP27" s="81"/>
-      <c r="BQ27" s="81"/>
-      <c r="BR27" s="81"/>
-      <c r="BS27" s="81"/>
-      <c r="BT27" s="81"/>
-      <c r="BU27" s="81"/>
-      <c r="BV27" s="81"/>
-      <c r="BW27" s="81"/>
-      <c r="BX27" s="81"/>
-      <c r="BY27" s="81"/>
-      <c r="BZ27" s="81"/>
-      <c r="CA27" s="81"/>
-      <c r="CB27" s="81"/>
-      <c r="CC27" s="81"/>
-      <c r="CD27" s="81"/>
-      <c r="CE27" s="81"/>
-      <c r="CF27" s="81"/>
-      <c r="CG27" s="81"/>
-      <c r="CH27" s="81"/>
-      <c r="CI27" s="81"/>
-      <c r="CJ27" s="81"/>
-      <c r="CK27" s="81"/>
-      <c r="CL27" s="81"/>
-      <c r="CM27" s="81"/>
-      <c r="CN27" s="81"/>
-      <c r="CO27" s="81"/>
-      <c r="CP27" s="81"/>
-      <c r="CQ27" s="81"/>
-      <c r="CR27" s="81"/>
-      <c r="CS27" s="81"/>
-      <c r="CT27" s="81"/>
-      <c r="CU27" s="81"/>
-      <c r="CV27" s="81"/>
-      <c r="CW27" s="81"/>
-      <c r="CX27" s="81"/>
-      <c r="CY27" s="81"/>
-      <c r="CZ27" s="81"/>
+      <c r="Y27" s="82"/>
+      <c r="Z27" s="82"/>
+      <c r="AA27" s="82"/>
+      <c r="AB27" s="82"/>
+      <c r="AC27" s="82"/>
+      <c r="AD27" s="82"/>
+      <c r="AE27" s="82"/>
+      <c r="AF27" s="82"/>
+      <c r="AG27" s="82"/>
+      <c r="AH27" s="82"/>
+      <c r="AI27" s="82"/>
+      <c r="AJ27" s="82"/>
+      <c r="AK27" s="82"/>
+      <c r="AL27" s="82"/>
+      <c r="AM27" s="82"/>
+      <c r="AN27" s="82"/>
+      <c r="AO27" s="82"/>
+      <c r="AP27" s="82"/>
+      <c r="AQ27" s="82"/>
+      <c r="AR27" s="82"/>
+      <c r="AS27" s="82"/>
+      <c r="AT27" s="82"/>
+      <c r="AU27" s="82"/>
+      <c r="AV27" s="82"/>
+      <c r="AW27" s="82"/>
+      <c r="AX27" s="82"/>
+      <c r="AY27" s="82"/>
+      <c r="AZ27" s="82"/>
+      <c r="BA27" s="82"/>
+      <c r="BB27" s="82"/>
+      <c r="BC27" s="82"/>
+      <c r="BD27" s="82"/>
+      <c r="BE27" s="82"/>
+      <c r="BF27" s="82"/>
+      <c r="BG27" s="82"/>
+      <c r="BH27" s="82"/>
+      <c r="BI27" s="82"/>
+      <c r="BJ27" s="82"/>
+      <c r="BK27" s="82"/>
+      <c r="BL27" s="82"/>
+      <c r="BM27" s="82"/>
+      <c r="BN27" s="82"/>
+      <c r="BO27" s="82"/>
+      <c r="BP27" s="82"/>
+      <c r="BQ27" s="82"/>
+      <c r="BR27" s="82"/>
+      <c r="BS27" s="82"/>
+      <c r="BT27" s="82"/>
+      <c r="BU27" s="82"/>
+      <c r="BV27" s="82"/>
+      <c r="BW27" s="82"/>
+      <c r="BX27" s="82"/>
+      <c r="BY27" s="82"/>
+      <c r="BZ27" s="82"/>
+      <c r="CA27" s="82"/>
+      <c r="CB27" s="82"/>
+      <c r="CC27" s="82"/>
+      <c r="CD27" s="82"/>
+      <c r="CE27" s="82"/>
+      <c r="CF27" s="82"/>
+      <c r="CG27" s="82"/>
+      <c r="CH27" s="82"/>
+      <c r="CI27" s="82"/>
+      <c r="CJ27" s="82"/>
+      <c r="CK27" s="82"/>
+      <c r="CL27" s="82"/>
+      <c r="CM27" s="82"/>
+      <c r="CN27" s="82"/>
+      <c r="CO27" s="82"/>
+      <c r="CP27" s="82"/>
+      <c r="CQ27" s="82"/>
+      <c r="CR27" s="82"/>
+      <c r="CS27" s="82"/>
+      <c r="CT27" s="82"/>
+      <c r="CU27" s="82"/>
+      <c r="CV27" s="82"/>
+      <c r="CW27" s="82"/>
+      <c r="CX27" s="82"/>
+      <c r="CY27" s="82"/>
+      <c r="CZ27" s="82"/>
     </row>
     <row r="28" spans="1:104" ht="35.25" customHeight="1">
       <c r="A28"/>
@@ -3236,16 +3267,16 @@
         <v>23</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F28" s="34" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G28" s="38">
         <v>12</v>
@@ -3273,86 +3304,86 @@
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
-      <c r="Y28" s="81"/>
-      <c r="Z28" s="81"/>
-      <c r="AA28" s="81"/>
-      <c r="AB28" s="81"/>
-      <c r="AC28" s="81"/>
-      <c r="AD28" s="81"/>
-      <c r="AE28" s="81"/>
-      <c r="AF28" s="81"/>
-      <c r="AG28" s="81"/>
-      <c r="AH28" s="81"/>
-      <c r="AI28" s="81"/>
-      <c r="AJ28" s="81"/>
-      <c r="AK28" s="81"/>
-      <c r="AL28" s="81"/>
-      <c r="AM28" s="81"/>
-      <c r="AN28" s="81"/>
-      <c r="AO28" s="81"/>
-      <c r="AP28" s="81"/>
-      <c r="AQ28" s="81"/>
-      <c r="AR28" s="81"/>
-      <c r="AS28" s="81"/>
-      <c r="AT28" s="81"/>
-      <c r="AU28" s="81"/>
-      <c r="AV28" s="81"/>
-      <c r="AW28" s="81"/>
-      <c r="AX28" s="81"/>
-      <c r="AY28" s="81"/>
-      <c r="AZ28" s="81"/>
-      <c r="BA28" s="81"/>
-      <c r="BB28" s="81"/>
-      <c r="BC28" s="81"/>
-      <c r="BD28" s="81"/>
-      <c r="BE28" s="81"/>
-      <c r="BF28" s="81"/>
-      <c r="BG28" s="81"/>
-      <c r="BH28" s="81"/>
-      <c r="BI28" s="81"/>
-      <c r="BJ28" s="81"/>
-      <c r="BK28" s="81"/>
-      <c r="BL28" s="81"/>
-      <c r="BM28" s="81"/>
-      <c r="BN28" s="81"/>
-      <c r="BO28" s="81"/>
-      <c r="BP28" s="81"/>
-      <c r="BQ28" s="81"/>
-      <c r="BR28" s="81"/>
-      <c r="BS28" s="81"/>
-      <c r="BT28" s="81"/>
-      <c r="BU28" s="81"/>
-      <c r="BV28" s="81"/>
-      <c r="BW28" s="81"/>
-      <c r="BX28" s="81"/>
-      <c r="BY28" s="81"/>
-      <c r="BZ28" s="81"/>
-      <c r="CA28" s="81"/>
-      <c r="CB28" s="81"/>
-      <c r="CC28" s="81"/>
-      <c r="CD28" s="81"/>
-      <c r="CE28" s="81"/>
-      <c r="CF28" s="81"/>
-      <c r="CG28" s="81"/>
-      <c r="CH28" s="81"/>
-      <c r="CI28" s="81"/>
-      <c r="CJ28" s="81"/>
-      <c r="CK28" s="81"/>
-      <c r="CL28" s="81"/>
-      <c r="CM28" s="81"/>
-      <c r="CN28" s="81"/>
-      <c r="CO28" s="81"/>
-      <c r="CP28" s="81"/>
-      <c r="CQ28" s="81"/>
-      <c r="CR28" s="81"/>
-      <c r="CS28" s="81"/>
-      <c r="CT28" s="81"/>
-      <c r="CU28" s="81"/>
-      <c r="CV28" s="81"/>
-      <c r="CW28" s="81"/>
-      <c r="CX28" s="81"/>
-      <c r="CY28" s="81"/>
-      <c r="CZ28" s="81"/>
+      <c r="Y28" s="82"/>
+      <c r="Z28" s="82"/>
+      <c r="AA28" s="82"/>
+      <c r="AB28" s="82"/>
+      <c r="AC28" s="82"/>
+      <c r="AD28" s="82"/>
+      <c r="AE28" s="82"/>
+      <c r="AF28" s="82"/>
+      <c r="AG28" s="82"/>
+      <c r="AH28" s="82"/>
+      <c r="AI28" s="82"/>
+      <c r="AJ28" s="82"/>
+      <c r="AK28" s="82"/>
+      <c r="AL28" s="82"/>
+      <c r="AM28" s="82"/>
+      <c r="AN28" s="82"/>
+      <c r="AO28" s="82"/>
+      <c r="AP28" s="82"/>
+      <c r="AQ28" s="82"/>
+      <c r="AR28" s="82"/>
+      <c r="AS28" s="82"/>
+      <c r="AT28" s="82"/>
+      <c r="AU28" s="82"/>
+      <c r="AV28" s="82"/>
+      <c r="AW28" s="82"/>
+      <c r="AX28" s="82"/>
+      <c r="AY28" s="82"/>
+      <c r="AZ28" s="82"/>
+      <c r="BA28" s="82"/>
+      <c r="BB28" s="82"/>
+      <c r="BC28" s="82"/>
+      <c r="BD28" s="82"/>
+      <c r="BE28" s="82"/>
+      <c r="BF28" s="82"/>
+      <c r="BG28" s="82"/>
+      <c r="BH28" s="82"/>
+      <c r="BI28" s="82"/>
+      <c r="BJ28" s="82"/>
+      <c r="BK28" s="82"/>
+      <c r="BL28" s="82"/>
+      <c r="BM28" s="82"/>
+      <c r="BN28" s="82"/>
+      <c r="BO28" s="82"/>
+      <c r="BP28" s="82"/>
+      <c r="BQ28" s="82"/>
+      <c r="BR28" s="82"/>
+      <c r="BS28" s="82"/>
+      <c r="BT28" s="82"/>
+      <c r="BU28" s="82"/>
+      <c r="BV28" s="82"/>
+      <c r="BW28" s="82"/>
+      <c r="BX28" s="82"/>
+      <c r="BY28" s="82"/>
+      <c r="BZ28" s="82"/>
+      <c r="CA28" s="82"/>
+      <c r="CB28" s="82"/>
+      <c r="CC28" s="82"/>
+      <c r="CD28" s="82"/>
+      <c r="CE28" s="82"/>
+      <c r="CF28" s="82"/>
+      <c r="CG28" s="82"/>
+      <c r="CH28" s="82"/>
+      <c r="CI28" s="82"/>
+      <c r="CJ28" s="82"/>
+      <c r="CK28" s="82"/>
+      <c r="CL28" s="82"/>
+      <c r="CM28" s="82"/>
+      <c r="CN28" s="82"/>
+      <c r="CO28" s="82"/>
+      <c r="CP28" s="82"/>
+      <c r="CQ28" s="82"/>
+      <c r="CR28" s="82"/>
+      <c r="CS28" s="82"/>
+      <c r="CT28" s="82"/>
+      <c r="CU28" s="82"/>
+      <c r="CV28" s="82"/>
+      <c r="CW28" s="82"/>
+      <c r="CX28" s="82"/>
+      <c r="CY28" s="82"/>
+      <c r="CZ28" s="82"/>
     </row>
     <row r="29" spans="1:104" ht="35.25" customHeight="1">
       <c r="A29"/>
@@ -3360,20 +3391,20 @@
         <v>24</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F29" s="33" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -3393,86 +3424,86 @@
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
       <c r="X29" s="9"/>
-      <c r="Y29" s="81"/>
-      <c r="Z29" s="81"/>
-      <c r="AA29" s="81"/>
-      <c r="AB29" s="81"/>
-      <c r="AC29" s="81"/>
-      <c r="AD29" s="81"/>
-      <c r="AE29" s="81"/>
-      <c r="AF29" s="81"/>
-      <c r="AG29" s="81"/>
-      <c r="AH29" s="81"/>
-      <c r="AI29" s="81"/>
-      <c r="AJ29" s="81"/>
-      <c r="AK29" s="81"/>
-      <c r="AL29" s="81"/>
-      <c r="AM29" s="81"/>
-      <c r="AN29" s="81"/>
-      <c r="AO29" s="81"/>
-      <c r="AP29" s="81"/>
-      <c r="AQ29" s="81"/>
-      <c r="AR29" s="81"/>
-      <c r="AS29" s="81"/>
-      <c r="AT29" s="81"/>
-      <c r="AU29" s="81"/>
-      <c r="AV29" s="81"/>
-      <c r="AW29" s="81"/>
-      <c r="AX29" s="81"/>
-      <c r="AY29" s="81"/>
-      <c r="AZ29" s="81"/>
-      <c r="BA29" s="81"/>
-      <c r="BB29" s="81"/>
-      <c r="BC29" s="81"/>
-      <c r="BD29" s="81"/>
-      <c r="BE29" s="81"/>
-      <c r="BF29" s="81"/>
-      <c r="BG29" s="81"/>
-      <c r="BH29" s="81"/>
-      <c r="BI29" s="81"/>
-      <c r="BJ29" s="81"/>
-      <c r="BK29" s="81"/>
-      <c r="BL29" s="81"/>
-      <c r="BM29" s="81"/>
-      <c r="BN29" s="81"/>
-      <c r="BO29" s="81"/>
-      <c r="BP29" s="81"/>
-      <c r="BQ29" s="81"/>
-      <c r="BR29" s="81"/>
-      <c r="BS29" s="81"/>
-      <c r="BT29" s="81"/>
-      <c r="BU29" s="81"/>
-      <c r="BV29" s="81"/>
-      <c r="BW29" s="81"/>
-      <c r="BX29" s="81"/>
-      <c r="BY29" s="81"/>
-      <c r="BZ29" s="81"/>
-      <c r="CA29" s="81"/>
-      <c r="CB29" s="81"/>
-      <c r="CC29" s="81"/>
-      <c r="CD29" s="81"/>
-      <c r="CE29" s="81"/>
-      <c r="CF29" s="81"/>
-      <c r="CG29" s="81"/>
-      <c r="CH29" s="81"/>
-      <c r="CI29" s="81"/>
-      <c r="CJ29" s="81"/>
-      <c r="CK29" s="81"/>
-      <c r="CL29" s="81"/>
-      <c r="CM29" s="81"/>
-      <c r="CN29" s="81"/>
-      <c r="CO29" s="81"/>
-      <c r="CP29" s="81"/>
-      <c r="CQ29" s="81"/>
-      <c r="CR29" s="81"/>
-      <c r="CS29" s="81"/>
-      <c r="CT29" s="81"/>
-      <c r="CU29" s="81"/>
-      <c r="CV29" s="81"/>
-      <c r="CW29" s="81"/>
-      <c r="CX29" s="81"/>
-      <c r="CY29" s="81"/>
-      <c r="CZ29" s="81"/>
+      <c r="Y29" s="82"/>
+      <c r="Z29" s="82"/>
+      <c r="AA29" s="82"/>
+      <c r="AB29" s="82"/>
+      <c r="AC29" s="82"/>
+      <c r="AD29" s="82"/>
+      <c r="AE29" s="82"/>
+      <c r="AF29" s="82"/>
+      <c r="AG29" s="82"/>
+      <c r="AH29" s="82"/>
+      <c r="AI29" s="82"/>
+      <c r="AJ29" s="82"/>
+      <c r="AK29" s="82"/>
+      <c r="AL29" s="82"/>
+      <c r="AM29" s="82"/>
+      <c r="AN29" s="82"/>
+      <c r="AO29" s="82"/>
+      <c r="AP29" s="82"/>
+      <c r="AQ29" s="82"/>
+      <c r="AR29" s="82"/>
+      <c r="AS29" s="82"/>
+      <c r="AT29" s="82"/>
+      <c r="AU29" s="82"/>
+      <c r="AV29" s="82"/>
+      <c r="AW29" s="82"/>
+      <c r="AX29" s="82"/>
+      <c r="AY29" s="82"/>
+      <c r="AZ29" s="82"/>
+      <c r="BA29" s="82"/>
+      <c r="BB29" s="82"/>
+      <c r="BC29" s="82"/>
+      <c r="BD29" s="82"/>
+      <c r="BE29" s="82"/>
+      <c r="BF29" s="82"/>
+      <c r="BG29" s="82"/>
+      <c r="BH29" s="82"/>
+      <c r="BI29" s="82"/>
+      <c r="BJ29" s="82"/>
+      <c r="BK29" s="82"/>
+      <c r="BL29" s="82"/>
+      <c r="BM29" s="82"/>
+      <c r="BN29" s="82"/>
+      <c r="BO29" s="82"/>
+      <c r="BP29" s="82"/>
+      <c r="BQ29" s="82"/>
+      <c r="BR29" s="82"/>
+      <c r="BS29" s="82"/>
+      <c r="BT29" s="82"/>
+      <c r="BU29" s="82"/>
+      <c r="BV29" s="82"/>
+      <c r="BW29" s="82"/>
+      <c r="BX29" s="82"/>
+      <c r="BY29" s="82"/>
+      <c r="BZ29" s="82"/>
+      <c r="CA29" s="82"/>
+      <c r="CB29" s="82"/>
+      <c r="CC29" s="82"/>
+      <c r="CD29" s="82"/>
+      <c r="CE29" s="82"/>
+      <c r="CF29" s="82"/>
+      <c r="CG29" s="82"/>
+      <c r="CH29" s="82"/>
+      <c r="CI29" s="82"/>
+      <c r="CJ29" s="82"/>
+      <c r="CK29" s="82"/>
+      <c r="CL29" s="82"/>
+      <c r="CM29" s="82"/>
+      <c r="CN29" s="82"/>
+      <c r="CO29" s="82"/>
+      <c r="CP29" s="82"/>
+      <c r="CQ29" s="82"/>
+      <c r="CR29" s="82"/>
+      <c r="CS29" s="82"/>
+      <c r="CT29" s="82"/>
+      <c r="CU29" s="82"/>
+      <c r="CV29" s="82"/>
+      <c r="CW29" s="82"/>
+      <c r="CX29" s="82"/>
+      <c r="CY29" s="82"/>
+      <c r="CZ29" s="82"/>
     </row>
     <row r="30" spans="1:104" ht="35.25" customHeight="1">
       <c r="A30"/>
@@ -3480,20 +3511,20 @@
         <v>25</v>
       </c>
       <c r="C30" s="61" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F30" s="34" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="56" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I30" s="56">
         <v>0</v>
@@ -3513,86 +3544,86 @@
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
       <c r="X30" s="9"/>
-      <c r="Y30" s="81"/>
-      <c r="Z30" s="81"/>
-      <c r="AA30" s="81"/>
-      <c r="AB30" s="81"/>
-      <c r="AC30" s="81"/>
-      <c r="AD30" s="81"/>
-      <c r="AE30" s="81"/>
-      <c r="AF30" s="81"/>
-      <c r="AG30" s="81"/>
-      <c r="AH30" s="81"/>
-      <c r="AI30" s="81"/>
-      <c r="AJ30" s="81"/>
-      <c r="AK30" s="81"/>
-      <c r="AL30" s="81"/>
-      <c r="AM30" s="81"/>
-      <c r="AN30" s="81"/>
-      <c r="AO30" s="81"/>
-      <c r="AP30" s="81"/>
-      <c r="AQ30" s="81"/>
-      <c r="AR30" s="81"/>
-      <c r="AS30" s="81"/>
-      <c r="AT30" s="81"/>
-      <c r="AU30" s="81"/>
-      <c r="AV30" s="81"/>
-      <c r="AW30" s="81"/>
-      <c r="AX30" s="81"/>
-      <c r="AY30" s="81"/>
-      <c r="AZ30" s="81"/>
-      <c r="BA30" s="81"/>
-      <c r="BB30" s="81"/>
-      <c r="BC30" s="81"/>
-      <c r="BD30" s="81"/>
-      <c r="BE30" s="81"/>
-      <c r="BF30" s="81"/>
-      <c r="BG30" s="81"/>
-      <c r="BH30" s="81"/>
-      <c r="BI30" s="81"/>
-      <c r="BJ30" s="81"/>
-      <c r="BK30" s="81"/>
-      <c r="BL30" s="81"/>
-      <c r="BM30" s="81"/>
-      <c r="BN30" s="81"/>
-      <c r="BO30" s="81"/>
-      <c r="BP30" s="81"/>
-      <c r="BQ30" s="81"/>
-      <c r="BR30" s="81"/>
-      <c r="BS30" s="81"/>
-      <c r="BT30" s="81"/>
-      <c r="BU30" s="81"/>
-      <c r="BV30" s="81"/>
-      <c r="BW30" s="81"/>
-      <c r="BX30" s="81"/>
-      <c r="BY30" s="81"/>
-      <c r="BZ30" s="81"/>
-      <c r="CA30" s="81"/>
-      <c r="CB30" s="81"/>
-      <c r="CC30" s="81"/>
-      <c r="CD30" s="81"/>
-      <c r="CE30" s="81"/>
-      <c r="CF30" s="81"/>
-      <c r="CG30" s="81"/>
-      <c r="CH30" s="81"/>
-      <c r="CI30" s="81"/>
-      <c r="CJ30" s="81"/>
-      <c r="CK30" s="81"/>
-      <c r="CL30" s="81"/>
-      <c r="CM30" s="81"/>
-      <c r="CN30" s="81"/>
-      <c r="CO30" s="81"/>
-      <c r="CP30" s="81"/>
-      <c r="CQ30" s="81"/>
-      <c r="CR30" s="81"/>
-      <c r="CS30" s="81"/>
-      <c r="CT30" s="81"/>
-      <c r="CU30" s="81"/>
-      <c r="CV30" s="81"/>
-      <c r="CW30" s="81"/>
-      <c r="CX30" s="81"/>
-      <c r="CY30" s="81"/>
-      <c r="CZ30" s="81"/>
+      <c r="Y30" s="82"/>
+      <c r="Z30" s="82"/>
+      <c r="AA30" s="82"/>
+      <c r="AB30" s="82"/>
+      <c r="AC30" s="82"/>
+      <c r="AD30" s="82"/>
+      <c r="AE30" s="82"/>
+      <c r="AF30" s="82"/>
+      <c r="AG30" s="82"/>
+      <c r="AH30" s="82"/>
+      <c r="AI30" s="82"/>
+      <c r="AJ30" s="82"/>
+      <c r="AK30" s="82"/>
+      <c r="AL30" s="82"/>
+      <c r="AM30" s="82"/>
+      <c r="AN30" s="82"/>
+      <c r="AO30" s="82"/>
+      <c r="AP30" s="82"/>
+      <c r="AQ30" s="82"/>
+      <c r="AR30" s="82"/>
+      <c r="AS30" s="82"/>
+      <c r="AT30" s="82"/>
+      <c r="AU30" s="82"/>
+      <c r="AV30" s="82"/>
+      <c r="AW30" s="82"/>
+      <c r="AX30" s="82"/>
+      <c r="AY30" s="82"/>
+      <c r="AZ30" s="82"/>
+      <c r="BA30" s="82"/>
+      <c r="BB30" s="82"/>
+      <c r="BC30" s="82"/>
+      <c r="BD30" s="82"/>
+      <c r="BE30" s="82"/>
+      <c r="BF30" s="82"/>
+      <c r="BG30" s="82"/>
+      <c r="BH30" s="82"/>
+      <c r="BI30" s="82"/>
+      <c r="BJ30" s="82"/>
+      <c r="BK30" s="82"/>
+      <c r="BL30" s="82"/>
+      <c r="BM30" s="82"/>
+      <c r="BN30" s="82"/>
+      <c r="BO30" s="82"/>
+      <c r="BP30" s="82"/>
+      <c r="BQ30" s="82"/>
+      <c r="BR30" s="82"/>
+      <c r="BS30" s="82"/>
+      <c r="BT30" s="82"/>
+      <c r="BU30" s="82"/>
+      <c r="BV30" s="82"/>
+      <c r="BW30" s="82"/>
+      <c r="BX30" s="82"/>
+      <c r="BY30" s="82"/>
+      <c r="BZ30" s="82"/>
+      <c r="CA30" s="82"/>
+      <c r="CB30" s="82"/>
+      <c r="CC30" s="82"/>
+      <c r="CD30" s="82"/>
+      <c r="CE30" s="82"/>
+      <c r="CF30" s="82"/>
+      <c r="CG30" s="82"/>
+      <c r="CH30" s="82"/>
+      <c r="CI30" s="82"/>
+      <c r="CJ30" s="82"/>
+      <c r="CK30" s="82"/>
+      <c r="CL30" s="82"/>
+      <c r="CM30" s="82"/>
+      <c r="CN30" s="82"/>
+      <c r="CO30" s="82"/>
+      <c r="CP30" s="82"/>
+      <c r="CQ30" s="82"/>
+      <c r="CR30" s="82"/>
+      <c r="CS30" s="82"/>
+      <c r="CT30" s="82"/>
+      <c r="CU30" s="82"/>
+      <c r="CV30" s="82"/>
+      <c r="CW30" s="82"/>
+      <c r="CX30" s="82"/>
+      <c r="CY30" s="82"/>
+      <c r="CZ30" s="82"/>
     </row>
     <row r="31" spans="1:104" ht="35.25" customHeight="1">
       <c r="A31"/>
@@ -3600,20 +3631,20 @@
         <v>26</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F31" s="33" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I31" s="3">
         <v>0</v>
@@ -3633,86 +3664,86 @@
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
       <c r="X31" s="9"/>
-      <c r="Y31" s="81"/>
-      <c r="Z31" s="81"/>
-      <c r="AA31" s="81"/>
-      <c r="AB31" s="81"/>
-      <c r="AC31" s="81"/>
-      <c r="AD31" s="81"/>
-      <c r="AE31" s="81"/>
-      <c r="AF31" s="81"/>
-      <c r="AG31" s="81"/>
-      <c r="AH31" s="81"/>
-      <c r="AI31" s="81"/>
-      <c r="AJ31" s="81"/>
-      <c r="AK31" s="81"/>
-      <c r="AL31" s="81"/>
-      <c r="AM31" s="81"/>
-      <c r="AN31" s="81"/>
-      <c r="AO31" s="81"/>
-      <c r="AP31" s="81"/>
-      <c r="AQ31" s="81"/>
-      <c r="AR31" s="81"/>
-      <c r="AS31" s="81"/>
-      <c r="AT31" s="81"/>
-      <c r="AU31" s="81"/>
-      <c r="AV31" s="81"/>
-      <c r="AW31" s="81"/>
-      <c r="AX31" s="81"/>
-      <c r="AY31" s="81"/>
-      <c r="AZ31" s="81"/>
-      <c r="BA31" s="81"/>
-      <c r="BB31" s="81"/>
-      <c r="BC31" s="81"/>
-      <c r="BD31" s="81"/>
-      <c r="BE31" s="81"/>
-      <c r="BF31" s="81"/>
-      <c r="BG31" s="81"/>
-      <c r="BH31" s="81"/>
-      <c r="BI31" s="81"/>
-      <c r="BJ31" s="81"/>
-      <c r="BK31" s="81"/>
-      <c r="BL31" s="81"/>
-      <c r="BM31" s="81"/>
-      <c r="BN31" s="81"/>
-      <c r="BO31" s="81"/>
-      <c r="BP31" s="81"/>
-      <c r="BQ31" s="81"/>
-      <c r="BR31" s="81"/>
-      <c r="BS31" s="81"/>
-      <c r="BT31" s="81"/>
-      <c r="BU31" s="81"/>
-      <c r="BV31" s="81"/>
-      <c r="BW31" s="81"/>
-      <c r="BX31" s="81"/>
-      <c r="BY31" s="81"/>
-      <c r="BZ31" s="81"/>
-      <c r="CA31" s="81"/>
-      <c r="CB31" s="81"/>
-      <c r="CC31" s="81"/>
-      <c r="CD31" s="81"/>
-      <c r="CE31" s="81"/>
-      <c r="CF31" s="81"/>
-      <c r="CG31" s="81"/>
-      <c r="CH31" s="81"/>
-      <c r="CI31" s="81"/>
-      <c r="CJ31" s="81"/>
-      <c r="CK31" s="81"/>
-      <c r="CL31" s="81"/>
-      <c r="CM31" s="81"/>
-      <c r="CN31" s="81"/>
-      <c r="CO31" s="81"/>
-      <c r="CP31" s="81"/>
-      <c r="CQ31" s="81"/>
-      <c r="CR31" s="81"/>
-      <c r="CS31" s="81"/>
-      <c r="CT31" s="81"/>
-      <c r="CU31" s="81"/>
-      <c r="CV31" s="81"/>
-      <c r="CW31" s="81"/>
-      <c r="CX31" s="81"/>
-      <c r="CY31" s="81"/>
-      <c r="CZ31" s="81"/>
+      <c r="Y31" s="82"/>
+      <c r="Z31" s="82"/>
+      <c r="AA31" s="82"/>
+      <c r="AB31" s="82"/>
+      <c r="AC31" s="82"/>
+      <c r="AD31" s="82"/>
+      <c r="AE31" s="82"/>
+      <c r="AF31" s="82"/>
+      <c r="AG31" s="82"/>
+      <c r="AH31" s="82"/>
+      <c r="AI31" s="82"/>
+      <c r="AJ31" s="82"/>
+      <c r="AK31" s="82"/>
+      <c r="AL31" s="82"/>
+      <c r="AM31" s="82"/>
+      <c r="AN31" s="82"/>
+      <c r="AO31" s="82"/>
+      <c r="AP31" s="82"/>
+      <c r="AQ31" s="82"/>
+      <c r="AR31" s="82"/>
+      <c r="AS31" s="82"/>
+      <c r="AT31" s="82"/>
+      <c r="AU31" s="82"/>
+      <c r="AV31" s="82"/>
+      <c r="AW31" s="82"/>
+      <c r="AX31" s="82"/>
+      <c r="AY31" s="82"/>
+      <c r="AZ31" s="82"/>
+      <c r="BA31" s="82"/>
+      <c r="BB31" s="82"/>
+      <c r="BC31" s="82"/>
+      <c r="BD31" s="82"/>
+      <c r="BE31" s="82"/>
+      <c r="BF31" s="82"/>
+      <c r="BG31" s="82"/>
+      <c r="BH31" s="82"/>
+      <c r="BI31" s="82"/>
+      <c r="BJ31" s="82"/>
+      <c r="BK31" s="82"/>
+      <c r="BL31" s="82"/>
+      <c r="BM31" s="82"/>
+      <c r="BN31" s="82"/>
+      <c r="BO31" s="82"/>
+      <c r="BP31" s="82"/>
+      <c r="BQ31" s="82"/>
+      <c r="BR31" s="82"/>
+      <c r="BS31" s="82"/>
+      <c r="BT31" s="82"/>
+      <c r="BU31" s="82"/>
+      <c r="BV31" s="82"/>
+      <c r="BW31" s="82"/>
+      <c r="BX31" s="82"/>
+      <c r="BY31" s="82"/>
+      <c r="BZ31" s="82"/>
+      <c r="CA31" s="82"/>
+      <c r="CB31" s="82"/>
+      <c r="CC31" s="82"/>
+      <c r="CD31" s="82"/>
+      <c r="CE31" s="82"/>
+      <c r="CF31" s="82"/>
+      <c r="CG31" s="82"/>
+      <c r="CH31" s="82"/>
+      <c r="CI31" s="82"/>
+      <c r="CJ31" s="82"/>
+      <c r="CK31" s="82"/>
+      <c r="CL31" s="82"/>
+      <c r="CM31" s="82"/>
+      <c r="CN31" s="82"/>
+      <c r="CO31" s="82"/>
+      <c r="CP31" s="82"/>
+      <c r="CQ31" s="82"/>
+      <c r="CR31" s="82"/>
+      <c r="CS31" s="82"/>
+      <c r="CT31" s="82"/>
+      <c r="CU31" s="82"/>
+      <c r="CV31" s="82"/>
+      <c r="CW31" s="82"/>
+      <c r="CX31" s="82"/>
+      <c r="CY31" s="82"/>
+      <c r="CZ31" s="82"/>
     </row>
     <row r="32" spans="1:104" ht="35.25" customHeight="1">
       <c r="A32"/>
@@ -3720,20 +3751,20 @@
         <v>27</v>
       </c>
       <c r="C32" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="57" t="s">
-        <v>73</v>
-      </c>
       <c r="E32" s="35" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F32" s="35" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="57" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I32" s="57">
         <v>0</v>
@@ -3753,294 +3784,294 @@
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
       <c r="X32" s="9"/>
-      <c r="Y32" s="81"/>
-      <c r="Z32" s="81"/>
-      <c r="AA32" s="81"/>
-      <c r="AB32" s="81"/>
-      <c r="AC32" s="81"/>
-      <c r="AD32" s="81"/>
-      <c r="AE32" s="81"/>
-      <c r="AF32" s="81"/>
-      <c r="AG32" s="81"/>
-      <c r="AH32" s="81"/>
-      <c r="AI32" s="81"/>
-      <c r="AJ32" s="81"/>
-      <c r="AK32" s="81"/>
-      <c r="AL32" s="81"/>
-      <c r="AM32" s="81"/>
-      <c r="AN32" s="81"/>
-      <c r="AO32" s="81"/>
-      <c r="AP32" s="81"/>
-      <c r="AQ32" s="81"/>
-      <c r="AR32" s="81"/>
-      <c r="AS32" s="81"/>
-      <c r="AT32" s="81"/>
-      <c r="AU32" s="81"/>
-      <c r="AV32" s="81"/>
-      <c r="AW32" s="81"/>
-      <c r="AX32" s="81"/>
-      <c r="AY32" s="81"/>
-      <c r="AZ32" s="81"/>
-      <c r="BA32" s="81"/>
-      <c r="BB32" s="81"/>
-      <c r="BC32" s="81"/>
-      <c r="BD32" s="81"/>
-      <c r="BE32" s="81"/>
-      <c r="BF32" s="81"/>
-      <c r="BG32" s="81"/>
-      <c r="BH32" s="81"/>
-      <c r="BI32" s="81"/>
-      <c r="BJ32" s="81"/>
-      <c r="BK32" s="81"/>
-      <c r="BL32" s="81"/>
-      <c r="BM32" s="81"/>
-      <c r="BN32" s="81"/>
-      <c r="BO32" s="81"/>
-      <c r="BP32" s="81"/>
-      <c r="BQ32" s="81"/>
-      <c r="BR32" s="81"/>
-      <c r="BS32" s="81"/>
-      <c r="BT32" s="81"/>
-      <c r="BU32" s="81"/>
-      <c r="BV32" s="81"/>
-      <c r="BW32" s="81"/>
-      <c r="BX32" s="81"/>
-      <c r="BY32" s="81"/>
-      <c r="BZ32" s="81"/>
-      <c r="CA32" s="81"/>
-      <c r="CB32" s="81"/>
-      <c r="CC32" s="81"/>
-      <c r="CD32" s="81"/>
-      <c r="CE32" s="81"/>
-      <c r="CF32" s="81"/>
-      <c r="CG32" s="81"/>
-      <c r="CH32" s="81"/>
-      <c r="CI32" s="81"/>
-      <c r="CJ32" s="81"/>
-      <c r="CK32" s="81"/>
-      <c r="CL32" s="81"/>
-      <c r="CM32" s="81"/>
-      <c r="CN32" s="81"/>
-      <c r="CO32" s="81"/>
-      <c r="CP32" s="81"/>
-      <c r="CQ32" s="81"/>
-      <c r="CR32" s="81"/>
-      <c r="CS32" s="81"/>
-      <c r="CT32" s="81"/>
-      <c r="CU32" s="81"/>
-      <c r="CV32" s="81"/>
-      <c r="CW32" s="81"/>
-      <c r="CX32" s="81"/>
-      <c r="CY32" s="81"/>
-      <c r="CZ32" s="81"/>
+      <c r="Y32" s="82"/>
+      <c r="Z32" s="82"/>
+      <c r="AA32" s="82"/>
+      <c r="AB32" s="82"/>
+      <c r="AC32" s="82"/>
+      <c r="AD32" s="82"/>
+      <c r="AE32" s="82"/>
+      <c r="AF32" s="82"/>
+      <c r="AG32" s="82"/>
+      <c r="AH32" s="82"/>
+      <c r="AI32" s="82"/>
+      <c r="AJ32" s="82"/>
+      <c r="AK32" s="82"/>
+      <c r="AL32" s="82"/>
+      <c r="AM32" s="82"/>
+      <c r="AN32" s="82"/>
+      <c r="AO32" s="82"/>
+      <c r="AP32" s="82"/>
+      <c r="AQ32" s="82"/>
+      <c r="AR32" s="82"/>
+      <c r="AS32" s="82"/>
+      <c r="AT32" s="82"/>
+      <c r="AU32" s="82"/>
+      <c r="AV32" s="82"/>
+      <c r="AW32" s="82"/>
+      <c r="AX32" s="82"/>
+      <c r="AY32" s="82"/>
+      <c r="AZ32" s="82"/>
+      <c r="BA32" s="82"/>
+      <c r="BB32" s="82"/>
+      <c r="BC32" s="82"/>
+      <c r="BD32" s="82"/>
+      <c r="BE32" s="82"/>
+      <c r="BF32" s="82"/>
+      <c r="BG32" s="82"/>
+      <c r="BH32" s="82"/>
+      <c r="BI32" s="82"/>
+      <c r="BJ32" s="82"/>
+      <c r="BK32" s="82"/>
+      <c r="BL32" s="82"/>
+      <c r="BM32" s="82"/>
+      <c r="BN32" s="82"/>
+      <c r="BO32" s="82"/>
+      <c r="BP32" s="82"/>
+      <c r="BQ32" s="82"/>
+      <c r="BR32" s="82"/>
+      <c r="BS32" s="82"/>
+      <c r="BT32" s="82"/>
+      <c r="BU32" s="82"/>
+      <c r="BV32" s="82"/>
+      <c r="BW32" s="82"/>
+      <c r="BX32" s="82"/>
+      <c r="BY32" s="82"/>
+      <c r="BZ32" s="82"/>
+      <c r="CA32" s="82"/>
+      <c r="CB32" s="82"/>
+      <c r="CC32" s="82"/>
+      <c r="CD32" s="82"/>
+      <c r="CE32" s="82"/>
+      <c r="CF32" s="82"/>
+      <c r="CG32" s="82"/>
+      <c r="CH32" s="82"/>
+      <c r="CI32" s="82"/>
+      <c r="CJ32" s="82"/>
+      <c r="CK32" s="82"/>
+      <c r="CL32" s="82"/>
+      <c r="CM32" s="82"/>
+      <c r="CN32" s="82"/>
+      <c r="CO32" s="82"/>
+      <c r="CP32" s="82"/>
+      <c r="CQ32" s="82"/>
+      <c r="CR32" s="82"/>
+      <c r="CS32" s="82"/>
+      <c r="CT32" s="82"/>
+      <c r="CU32" s="82"/>
+      <c r="CV32" s="82"/>
+      <c r="CW32" s="82"/>
+      <c r="CX32" s="82"/>
+      <c r="CY32" s="82"/>
+      <c r="CZ32" s="82"/>
     </row>
     <row r="33" spans="3:104" ht="35.25" customHeight="1">
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-      <c r="K33" s="81"/>
-      <c r="L33" s="81"/>
-      <c r="M33" s="81"/>
-      <c r="N33" s="81"/>
-      <c r="O33" s="81"/>
-      <c r="P33" s="81"/>
-      <c r="Q33" s="81"/>
-      <c r="R33" s="81"/>
-      <c r="S33" s="81"/>
-      <c r="T33" s="81"/>
-      <c r="U33" s="81"/>
-      <c r="V33" s="81"/>
-      <c r="W33" s="81"/>
-      <c r="X33" s="81"/>
-      <c r="Y33" s="81"/>
-      <c r="Z33" s="81"/>
-      <c r="AA33" s="81"/>
-      <c r="AB33" s="81"/>
-      <c r="AC33" s="81"/>
-      <c r="AD33" s="81"/>
-      <c r="AE33" s="81"/>
-      <c r="AF33" s="81"/>
-      <c r="AG33" s="81"/>
-      <c r="AH33" s="81"/>
-      <c r="AI33" s="81"/>
-      <c r="AJ33" s="81"/>
-      <c r="AK33" s="81"/>
-      <c r="AL33" s="81"/>
-      <c r="AM33" s="81"/>
-      <c r="AN33" s="81"/>
-      <c r="AO33" s="81"/>
-      <c r="AP33" s="81"/>
-      <c r="AQ33" s="81"/>
-      <c r="AR33" s="81"/>
-      <c r="AS33" s="81"/>
-      <c r="AT33" s="81"/>
-      <c r="AU33" s="81"/>
-      <c r="AV33" s="81"/>
-      <c r="AW33" s="81"/>
-      <c r="AX33" s="81"/>
-      <c r="AY33" s="81"/>
-      <c r="AZ33" s="81"/>
-      <c r="BA33" s="81"/>
-      <c r="BB33" s="81"/>
-      <c r="BC33" s="81"/>
-      <c r="BD33" s="81"/>
-      <c r="BE33" s="81"/>
-      <c r="BF33" s="81"/>
-      <c r="BG33" s="81"/>
-      <c r="BH33" s="81"/>
-      <c r="BI33" s="81"/>
-      <c r="BJ33" s="81"/>
-      <c r="BK33" s="81"/>
-      <c r="BL33" s="81"/>
-      <c r="BM33" s="81"/>
-      <c r="BN33" s="81"/>
-      <c r="BO33" s="81"/>
-      <c r="BP33" s="81"/>
-      <c r="BQ33" s="81"/>
-      <c r="BR33" s="81"/>
-      <c r="BS33" s="81"/>
-      <c r="BT33" s="81"/>
-      <c r="BU33" s="81"/>
-      <c r="BV33" s="81"/>
-      <c r="BW33" s="81"/>
-      <c r="BX33" s="81"/>
-      <c r="BY33" s="81"/>
-      <c r="BZ33" s="81"/>
-      <c r="CA33" s="81"/>
-      <c r="CB33" s="81"/>
-      <c r="CC33" s="81"/>
-      <c r="CD33" s="81"/>
-      <c r="CE33" s="81"/>
-      <c r="CF33" s="81"/>
-      <c r="CG33" s="81"/>
-      <c r="CH33" s="81"/>
-      <c r="CI33" s="81"/>
-      <c r="CJ33" s="81"/>
-      <c r="CK33" s="81"/>
-      <c r="CL33" s="81"/>
-      <c r="CM33" s="81"/>
-      <c r="CN33" s="81"/>
-      <c r="CO33" s="81"/>
-      <c r="CP33" s="81"/>
-      <c r="CQ33" s="81"/>
-      <c r="CR33" s="81"/>
-      <c r="CS33" s="81"/>
-      <c r="CT33" s="81"/>
-      <c r="CU33" s="81"/>
-      <c r="CV33" s="81"/>
-      <c r="CW33" s="81"/>
-      <c r="CX33" s="81"/>
-      <c r="CY33" s="81"/>
-      <c r="CZ33" s="81"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
+      <c r="M33" s="82"/>
+      <c r="N33" s="82"/>
+      <c r="O33" s="82"/>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="82"/>
+      <c r="T33" s="82"/>
+      <c r="U33" s="82"/>
+      <c r="V33" s="82"/>
+      <c r="W33" s="82"/>
+      <c r="X33" s="82"/>
+      <c r="Y33" s="82"/>
+      <c r="Z33" s="82"/>
+      <c r="AA33" s="82"/>
+      <c r="AB33" s="82"/>
+      <c r="AC33" s="82"/>
+      <c r="AD33" s="82"/>
+      <c r="AE33" s="82"/>
+      <c r="AF33" s="82"/>
+      <c r="AG33" s="82"/>
+      <c r="AH33" s="82"/>
+      <c r="AI33" s="82"/>
+      <c r="AJ33" s="82"/>
+      <c r="AK33" s="82"/>
+      <c r="AL33" s="82"/>
+      <c r="AM33" s="82"/>
+      <c r="AN33" s="82"/>
+      <c r="AO33" s="82"/>
+      <c r="AP33" s="82"/>
+      <c r="AQ33" s="82"/>
+      <c r="AR33" s="82"/>
+      <c r="AS33" s="82"/>
+      <c r="AT33" s="82"/>
+      <c r="AU33" s="82"/>
+      <c r="AV33" s="82"/>
+      <c r="AW33" s="82"/>
+      <c r="AX33" s="82"/>
+      <c r="AY33" s="82"/>
+      <c r="AZ33" s="82"/>
+      <c r="BA33" s="82"/>
+      <c r="BB33" s="82"/>
+      <c r="BC33" s="82"/>
+      <c r="BD33" s="82"/>
+      <c r="BE33" s="82"/>
+      <c r="BF33" s="82"/>
+      <c r="BG33" s="82"/>
+      <c r="BH33" s="82"/>
+      <c r="BI33" s="82"/>
+      <c r="BJ33" s="82"/>
+      <c r="BK33" s="82"/>
+      <c r="BL33" s="82"/>
+      <c r="BM33" s="82"/>
+      <c r="BN33" s="82"/>
+      <c r="BO33" s="82"/>
+      <c r="BP33" s="82"/>
+      <c r="BQ33" s="82"/>
+      <c r="BR33" s="82"/>
+      <c r="BS33" s="82"/>
+      <c r="BT33" s="82"/>
+      <c r="BU33" s="82"/>
+      <c r="BV33" s="82"/>
+      <c r="BW33" s="82"/>
+      <c r="BX33" s="82"/>
+      <c r="BY33" s="82"/>
+      <c r="BZ33" s="82"/>
+      <c r="CA33" s="82"/>
+      <c r="CB33" s="82"/>
+      <c r="CC33" s="82"/>
+      <c r="CD33" s="82"/>
+      <c r="CE33" s="82"/>
+      <c r="CF33" s="82"/>
+      <c r="CG33" s="82"/>
+      <c r="CH33" s="82"/>
+      <c r="CI33" s="82"/>
+      <c r="CJ33" s="82"/>
+      <c r="CK33" s="82"/>
+      <c r="CL33" s="82"/>
+      <c r="CM33" s="82"/>
+      <c r="CN33" s="82"/>
+      <c r="CO33" s="82"/>
+      <c r="CP33" s="82"/>
+      <c r="CQ33" s="82"/>
+      <c r="CR33" s="82"/>
+      <c r="CS33" s="82"/>
+      <c r="CT33" s="82"/>
+      <c r="CU33" s="82"/>
+      <c r="CV33" s="82"/>
+      <c r="CW33" s="82"/>
+      <c r="CX33" s="82"/>
+      <c r="CY33" s="82"/>
+      <c r="CZ33" s="82"/>
     </row>
     <row r="34" spans="3:104" ht="35.25" customHeight="1">
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="81"/>
-      <c r="L34" s="81"/>
-      <c r="M34" s="81"/>
-      <c r="N34" s="81"/>
-      <c r="O34" s="81"/>
-      <c r="P34" s="81"/>
-      <c r="Q34" s="81"/>
-      <c r="R34" s="81"/>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="81"/>
-      <c r="V34" s="81"/>
-      <c r="W34" s="81"/>
-      <c r="X34" s="81"/>
-      <c r="Y34" s="81"/>
-      <c r="Z34" s="81"/>
-      <c r="AA34" s="81"/>
-      <c r="AB34" s="81"/>
-      <c r="AC34" s="81"/>
-      <c r="AD34" s="81"/>
-      <c r="AE34" s="81"/>
-      <c r="AF34" s="81"/>
-      <c r="AG34" s="81"/>
-      <c r="AH34" s="81"/>
-      <c r="AI34" s="81"/>
-      <c r="AJ34" s="81"/>
-      <c r="AK34" s="81"/>
-      <c r="AL34" s="81"/>
-      <c r="AM34" s="81"/>
-      <c r="AN34" s="81"/>
-      <c r="AO34" s="81"/>
-      <c r="AP34" s="81"/>
-      <c r="AQ34" s="81"/>
-      <c r="AR34" s="81"/>
-      <c r="AS34" s="81"/>
-      <c r="AT34" s="81"/>
-      <c r="AU34" s="81"/>
-      <c r="AV34" s="81"/>
-      <c r="AW34" s="81"/>
-      <c r="AX34" s="81"/>
-      <c r="AY34" s="81"/>
-      <c r="AZ34" s="81"/>
-      <c r="BA34" s="81"/>
-      <c r="BB34" s="81"/>
-      <c r="BC34" s="81"/>
-      <c r="BD34" s="81"/>
-      <c r="BE34" s="81"/>
-      <c r="BF34" s="81"/>
-      <c r="BG34" s="81"/>
-      <c r="BH34" s="81"/>
-      <c r="BI34" s="81"/>
-      <c r="BJ34" s="81"/>
-      <c r="BK34" s="81"/>
-      <c r="BL34" s="81"/>
-      <c r="BM34" s="81"/>
-      <c r="BN34" s="81"/>
-      <c r="BO34" s="81"/>
-      <c r="BP34" s="81"/>
-      <c r="BQ34" s="81"/>
-      <c r="BR34" s="81"/>
-      <c r="BS34" s="81"/>
-      <c r="BT34" s="81"/>
-      <c r="BU34" s="81"/>
-      <c r="BV34" s="81"/>
-      <c r="BW34" s="81"/>
-      <c r="BX34" s="81"/>
-      <c r="BY34" s="81"/>
-      <c r="BZ34" s="81"/>
-      <c r="CA34" s="81"/>
-      <c r="CB34" s="81"/>
-      <c r="CC34" s="81"/>
-      <c r="CD34" s="81"/>
-      <c r="CE34" s="81"/>
-      <c r="CF34" s="81"/>
-      <c r="CG34" s="81"/>
-      <c r="CH34" s="81"/>
-      <c r="CI34" s="81"/>
-      <c r="CJ34" s="81"/>
-      <c r="CK34" s="81"/>
-      <c r="CL34" s="81"/>
-      <c r="CM34" s="81"/>
-      <c r="CN34" s="81"/>
-      <c r="CO34" s="81"/>
-      <c r="CP34" s="81"/>
-      <c r="CQ34" s="81"/>
-      <c r="CR34" s="81"/>
-      <c r="CS34" s="81"/>
-      <c r="CT34" s="81"/>
-      <c r="CU34" s="81"/>
-      <c r="CV34" s="81"/>
-      <c r="CW34" s="81"/>
-      <c r="CX34" s="81"/>
-      <c r="CY34" s="81"/>
-      <c r="CZ34" s="81"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
+      <c r="M34" s="82"/>
+      <c r="N34" s="82"/>
+      <c r="O34" s="82"/>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="82"/>
+      <c r="V34" s="82"/>
+      <c r="W34" s="82"/>
+      <c r="X34" s="82"/>
+      <c r="Y34" s="82"/>
+      <c r="Z34" s="82"/>
+      <c r="AA34" s="82"/>
+      <c r="AB34" s="82"/>
+      <c r="AC34" s="82"/>
+      <c r="AD34" s="82"/>
+      <c r="AE34" s="82"/>
+      <c r="AF34" s="82"/>
+      <c r="AG34" s="82"/>
+      <c r="AH34" s="82"/>
+      <c r="AI34" s="82"/>
+      <c r="AJ34" s="82"/>
+      <c r="AK34" s="82"/>
+      <c r="AL34" s="82"/>
+      <c r="AM34" s="82"/>
+      <c r="AN34" s="82"/>
+      <c r="AO34" s="82"/>
+      <c r="AP34" s="82"/>
+      <c r="AQ34" s="82"/>
+      <c r="AR34" s="82"/>
+      <c r="AS34" s="82"/>
+      <c r="AT34" s="82"/>
+      <c r="AU34" s="82"/>
+      <c r="AV34" s="82"/>
+      <c r="AW34" s="82"/>
+      <c r="AX34" s="82"/>
+      <c r="AY34" s="82"/>
+      <c r="AZ34" s="82"/>
+      <c r="BA34" s="82"/>
+      <c r="BB34" s="82"/>
+      <c r="BC34" s="82"/>
+      <c r="BD34" s="82"/>
+      <c r="BE34" s="82"/>
+      <c r="BF34" s="82"/>
+      <c r="BG34" s="82"/>
+      <c r="BH34" s="82"/>
+      <c r="BI34" s="82"/>
+      <c r="BJ34" s="82"/>
+      <c r="BK34" s="82"/>
+      <c r="BL34" s="82"/>
+      <c r="BM34" s="82"/>
+      <c r="BN34" s="82"/>
+      <c r="BO34" s="82"/>
+      <c r="BP34" s="82"/>
+      <c r="BQ34" s="82"/>
+      <c r="BR34" s="82"/>
+      <c r="BS34" s="82"/>
+      <c r="BT34" s="82"/>
+      <c r="BU34" s="82"/>
+      <c r="BV34" s="82"/>
+      <c r="BW34" s="82"/>
+      <c r="BX34" s="82"/>
+      <c r="BY34" s="82"/>
+      <c r="BZ34" s="82"/>
+      <c r="CA34" s="82"/>
+      <c r="CB34" s="82"/>
+      <c r="CC34" s="82"/>
+      <c r="CD34" s="82"/>
+      <c r="CE34" s="82"/>
+      <c r="CF34" s="82"/>
+      <c r="CG34" s="82"/>
+      <c r="CH34" s="82"/>
+      <c r="CI34" s="82"/>
+      <c r="CJ34" s="82"/>
+      <c r="CK34" s="82"/>
+      <c r="CL34" s="82"/>
+      <c r="CM34" s="82"/>
+      <c r="CN34" s="82"/>
+      <c r="CO34" s="82"/>
+      <c r="CP34" s="82"/>
+      <c r="CQ34" s="82"/>
+      <c r="CR34" s="82"/>
+      <c r="CS34" s="82"/>
+      <c r="CT34" s="82"/>
+      <c r="CU34" s="82"/>
+      <c r="CV34" s="82"/>
+      <c r="CW34" s="82"/>
+      <c r="CX34" s="82"/>
+      <c r="CY34" s="82"/>
+      <c r="CZ34" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="6">
